--- a/static/excel/TSLA_model.xlsx
+++ b/static/excel/TSLA_model.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="175" formatCode="0.000"/>
     <numFmt numFmtId="176" formatCode="0.00;(0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -221,12 +221,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001565C0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
@@ -236,7 +230,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -328,11 +322,6 @@
         <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -360,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -756,9 +745,6 @@
     <xf numFmtId="0" fontId="30" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -766,13 +752,13 @@
     <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -7416,11 +7402,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7431,7 +7417,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7630,25 +7616,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0539</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A4CBBBEY — BBB</t>
         </is>
       </c>
     </row>
@@ -7691,11 +7679,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.54%</t>
+          <t>Rf 4.56% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7734,11 +7722,11 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0463</v>
+        <v>0.0488</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10053,7 +10041,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — TSLA  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — TSLA  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10558,7 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Current 382.3x  |  5yr avg 167.1x  |  DCF-implied 2.4x [ref only — not used as benchmark]  [+129% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→1.93 | abs=0.0 → blended 40/40/20=0.77]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 210.1x  |  DCF-implied 2.4x [ref only — not used as benchmark]  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="130" t="inlineStr">
@@ -10579,7 +10567,7 @@
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10587,7 +10575,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Current 382.3x  |  5yr avg 167.1x  |  DCF-implied 2.4x [ref only — not used as benchmark]  [+129% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→1.93 | abs=0.0 → blended 40/40/20=0.77]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 210.1x  |  DCF-implied 2.4x [ref only — not used as benchmark]  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10607,16 +10595,16 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 233.2x  |  5yr avg 225.0x  |  DCF-implied 1.5x [ref only — not used as benchmark]  [+4% vs benchmark]  [trail=6.42 | fwd_pfcf=203.8x→8.41 | abs=0.0 → blended 40/40/20=5.93]  [fcf_yield=0.4% vs rf=4.6%  spread=-4.1%→modifier=-0.50]</t>
-        </is>
-      </c>
-      <c r="E23" s="135" t="inlineStr">
-        <is>
-          <t>MOD-HIGH</t>
+          <t>Current 233.2x  |  5yr avg 226.6x  |  DCF-implied 1.5x [ref only — not used as benchmark]  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.6%  spread=-4.1%→modifier=-0.50]</t>
+        </is>
+      </c>
+      <c r="E23" s="130" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F23" s="131" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="G23" s="132">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10624,7 +10612,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 233.2x  |  5yr avg 225.0x  |  DCF-implied 1.5x [ref only — not used as benchmark]  [+4% vs benchmark]  [trail=6.42 | fwd_pfcf=203.8x→8.41 | abs=0.0 → blended 40/40/20=5.93]  [fcf_yield=0.4% vs rf=4.6%  spread=-4.1%→modifier=-0.50]</t>
+          <t>Current 233.2x  |  5yr avg 226.6x  |  DCF-implied 1.5x [ref only — not used as benchmark]  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.6%  spread=-4.1%→modifier=-0.50]</t>
         </is>
       </c>
     </row>
@@ -10639,21 +10627,21 @@
       <c r="H24" s="42" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="136" t="inlineStr">
+      <c r="A25" s="135" t="inlineStr">
         <is>
           <t>TOTAL SCORE  (max = 100.0)</t>
         </is>
       </c>
-      <c r="B25" s="137" t="n"/>
-      <c r="C25" s="137" t="n"/>
-      <c r="D25" s="137" t="n"/>
-      <c r="E25" s="137" t="n"/>
-      <c r="F25" s="137" t="n"/>
-      <c r="G25" s="138">
+      <c r="B25" s="136" t="n"/>
+      <c r="C25" s="136" t="n"/>
+      <c r="D25" s="136" t="n"/>
+      <c r="E25" s="136" t="n"/>
+      <c r="F25" s="136" t="n"/>
+      <c r="G25" s="137">
         <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
         <v/>
       </c>
-      <c r="H25" s="139" t="inlineStr">
+      <c r="H25" s="138" t="inlineStr">
         <is>
           <t>No floor cap.</t>
         </is>
@@ -10670,7 +10658,7 @@
       <c r="H26" s="42" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="140">
+      <c r="A27" s="139">
         <f>IF(G25="","Score incomplete — fill qualitative tiers above",IF(G25&gt;=80,"STRONG BUY",IF(G25&gt;=65,"BUY",IF(G25&gt;=50,"HOLD",IF(G25&gt;=35,"REDUCE","SELL")))))</f>
         <v/>
       </c>
@@ -10686,7 +10674,7 @@
       <c r="H28" s="42" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="141" t="inlineStr">
+      <c r="A29" s="140" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>

--- a/static/excel/TSLA_model.xlsx
+++ b/static/excel/TSLA_model.xlsx
@@ -7402,11 +7402,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0446</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-22</t>
+          <t>FRED series DGS10  |  latest: 2026-06-18</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0456</v>
+        <v>0.0446</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="B32" s="46" t="n">
-        <v>0.0539</v>
+        <v>0.0535</v>
       </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
@@ -7679,11 +7679,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.56% + spread 0.54%</t>
+          <t>Rf 4.46% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0488</v>
+        <v>0.0484</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -8159,13 +8159,13 @@
         <v/>
       </c>
       <c r="G7" s="71" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="H7" s="71" t="n">
-        <v>0.1481</v>
+        <v>0.1488</v>
       </c>
       <c r="I7" s="71" t="n">
-        <v>0.1829</v>
+        <v>0.1803</v>
       </c>
       <c r="J7" s="72">
         <f>I7</f>
@@ -8509,13 +8509,13 @@
         <v/>
       </c>
       <c r="G15" s="77" t="n">
-        <v>102749.9</v>
+        <v>102413</v>
       </c>
       <c r="H15" s="77" t="n">
-        <v>117971.5</v>
+        <v>117657</v>
       </c>
       <c r="I15" s="77" t="n">
-        <v>139544.1</v>
+        <v>138867.5</v>
       </c>
       <c r="J15" s="78">
         <f>I15*(1+J7)</f>
@@ -8543,27 +8543,27 @@
       </c>
       <c r="G16" s="82" t="inlineStr">
         <is>
-          <t>91,605 — 113,987</t>
+          <t>93,652 — 113,018</t>
         </is>
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>104,960 — 132,105</t>
+          <t>103,850 — 130,707</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
         <is>
-          <t>138,786 — 140,302</t>
+          <t>138,853 — 138,882</t>
         </is>
       </c>
       <c r="J16" s="82" t="inlineStr">
         <is>
-          <t>195,786 — 267,639</t>
+          <t>197,780 — 266,447</t>
         </is>
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>207,938 — 284,251</t>
+          <t>210,055 — 282,984</t>
         </is>
       </c>
       <c r="L16" s="83" t="inlineStr">
@@ -8590,13 +8590,13 @@
         <v>35</v>
       </c>
       <c r="I17" s="84" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J17" s="84" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K17" s="84" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L17" s="83" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         <v/>
       </c>
       <c r="G20" s="77" t="n">
-        <v>16914.4</v>
+        <v>16859</v>
       </c>
       <c r="H20" s="77" t="n">
-        <v>19420.2</v>
+        <v>19368.4</v>
       </c>
       <c r="I20" s="77" t="n">
-        <v>22971.4</v>
+        <v>22860</v>
       </c>
       <c r="J20" s="78">
         <f>J15*J8</f>
@@ -8741,27 +8741,27 @@
       </c>
       <c r="G21" s="82" t="inlineStr">
         <is>
-          <t>15,080 — 18,764</t>
+          <t>15,417 — 18,605</t>
         </is>
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>17,278 — 21,747</t>
+          <t>17,095 — 21,517</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
         <is>
-          <t>22,847 — 23,096</t>
+          <t>22,858 — 22,862</t>
         </is>
       </c>
       <c r="J21" s="82" t="inlineStr">
         <is>
-          <t>32,230 — 44,058</t>
+          <t>32,558 — 43,862</t>
         </is>
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>34,230 — 46,793</t>
+          <t>34,579 — 46,584</t>
         </is>
       </c>
       <c r="L21" s="83" t="inlineStr">
@@ -10041,7 +10041,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — TSLA  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — TSLA  |  Master Prompt v2  |  23 Jun 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="D9" s="129" t="inlineStr">
         <is>
-          <t>GM 18.0% ✗ (&gt;40%)  |  GM trend -7.6% ✗ (&gt;+1pp)  |  ROIC-WACC -8.0% ✗ (&gt;+5pp)  |  Rev consistency σ=21.4% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
+          <t>GM 18.0% ✗ (&gt;40%)  |  GM trend -7.6% ✗ (&gt;+1pp)  |  ROIC-WACC -7.9% ✗ (&gt;+5pp)  |  Rev consistency σ=21.4% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="130" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H9" s="133" t="inlineStr">
         <is>
-          <t>GM 18.0% ✗ (&gt;40%)  |  GM trend -7.6% ✗ (&gt;+1pp)  |  ROIC-WACC -8.0% ✗ (&gt;+5pp)  |  Rev consistency σ=21.4% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
+          <t>GM 18.0% ✗ (&gt;40%)  |  GM trend -7.6% ✗ (&gt;+1pp)  |  ROIC-WACC -7.9% ✗ (&gt;+5pp)  |  Rev consistency σ=21.4% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 210.1x  |  DCF-implied 2.4x [ref only — not used as benchmark]  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 212.8x  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="130" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 210.1x  |  DCF-implied 2.4x [ref only — not used as benchmark]  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 212.8x  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 233.2x  |  5yr avg 226.6x  |  DCF-implied 1.5x [ref only — not used as benchmark]  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.6%  spread=-4.1%→modifier=-0.50]</t>
+          <t>Current 233.2x  |  5yr avg 227.9x  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.5%  spread=-4.0%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="130" t="inlineStr">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 233.2x  |  5yr avg 226.6x  |  DCF-implied 1.5x [ref only — not used as benchmark]  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.6%  spread=-4.1%→modifier=-0.50]</t>
+          <t>Current 233.2x  |  5yr avg 227.9x  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.5%  spread=-4.0%→modifier=-0.50]</t>
         </is>
       </c>
     </row>

--- a/static/excel/TSLA_model.xlsx
+++ b/static/excel/TSLA_model.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="175" formatCode="0.000"/>
     <numFmt numFmtId="176" formatCode="0.00;(0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -136,18 +136,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001A5276"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="00999999"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001A5276"/>
       <sz val="10"/>
     </font>
     <font>
@@ -294,17 +283,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4E6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EBF5FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FBFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4E6F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -349,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -535,175 +524,160 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="20" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="22" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="175" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="175" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,31 +692,31 @@
     <xf numFmtId="0" fontId="13" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="176" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="176" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -752,13 +726,13 @@
     <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -8003,7 +7977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8102,1918 +8076,1926 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>FMP analyst consensus: 2026E – 2030E  (5 years)   |   User estimates required from: N/AE onwards</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="6" customHeight="1">
-      <c r="A5" s="42" t="n"/>
-      <c r="B5" s="42" t="n"/>
-      <c r="C5" s="42" t="n"/>
-      <c r="D5" s="42" t="n"/>
-      <c r="E5" s="42" t="n"/>
-      <c r="F5" s="42" t="n"/>
-      <c r="G5" s="42" t="n"/>
-      <c r="H5" s="42" t="n"/>
-      <c r="I5" s="42" t="n"/>
-      <c r="J5" s="42" t="n"/>
-      <c r="K5" s="42" t="n"/>
-      <c r="L5" s="42" t="n"/>
-      <c r="M5" s="42" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="42" t="n"/>
+      <c r="B4" s="42" t="n"/>
+      <c r="C4" s="42" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+      <c r="G4" s="42" t="n"/>
+      <c r="H4" s="42" t="n"/>
+      <c r="I4" s="42" t="n"/>
+      <c r="J4" s="42" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="42" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>SECTION 1 — PROJECTION ASSUMPTIONS  (darker blue = FMP consensus-derived  |  lighter blue = user input)</t>
         </is>
       </c>
     </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="67" t="inlineStr">
+        <is>
+          <t>Revenue Growth %</t>
+        </is>
+      </c>
+      <c r="B6" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="69">
+        <f>'P&amp;L'!C5/'P&amp;L'!B5-1</f>
+        <v/>
+      </c>
+      <c r="D6" s="69">
+        <f>'P&amp;L'!D5/'P&amp;L'!C5-1</f>
+        <v/>
+      </c>
+      <c r="E6" s="69">
+        <f>'P&amp;L'!E5/'P&amp;L'!D5-1</f>
+        <v/>
+      </c>
+      <c r="F6" s="69">
+        <f>'P&amp;L'!F5/'P&amp;L'!E5-1</f>
+        <v/>
+      </c>
+      <c r="G6" s="70" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H6" s="70" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I6" s="70" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J6" s="70">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="K6" s="70">
+        <f>I6</f>
+        <v/>
+      </c>
+      <c r="L6" s="71" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M6" s="72" t="inlineStr">
+        <is>
+          <t>Yrs 1-3: FMP analyst consensus implied growth (back-calc from rev estimates).  Yrs 4-5: formula = Yr 3 growth.  Terminal = long-run growth (2-4%).</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="68" t="inlineStr">
-        <is>
-          <t>Revenue Growth %</t>
-        </is>
-      </c>
-      <c r="B7" s="69" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
+        <is>
+          <t>EBITDA Margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="69">
+        <f>'P&amp;L'!B12/'P&amp;L'!B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="69">
+        <f>'P&amp;L'!C12/'P&amp;L'!C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="69">
+        <f>'P&amp;L'!D12/'P&amp;L'!D5</f>
+        <v/>
+      </c>
+      <c r="E7" s="69">
+        <f>'P&amp;L'!E12/'P&amp;L'!E5</f>
+        <v/>
+      </c>
+      <c r="F7" s="69">
+        <f>'P&amp;L'!F12/'P&amp;L'!F5</f>
+        <v/>
+      </c>
+      <c r="G7" s="70" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="H7" s="70" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="I7" s="70" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="J7" s="70">
+        <f>I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="70">
+        <f>I7</f>
+        <v/>
+      </c>
+      <c r="L7" s="71" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="M7" s="72" t="inlineStr">
+        <is>
+          <t>Yrs 1-3: FMP analyst consensus margin.  Yrs 4-5: = Yr 3 margin.  Terminal: long-run normalised EBITDA margin (user input).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="67" t="inlineStr">
+        <is>
+          <t>D&amp;A as % of Revenue</t>
+        </is>
+      </c>
+      <c r="B8" s="69">
+        <f>'P&amp;L'!B14/'P&amp;L'!B5</f>
+        <v/>
+      </c>
+      <c r="C8" s="69">
+        <f>'P&amp;L'!C14/'P&amp;L'!C5</f>
+        <v/>
+      </c>
+      <c r="D8" s="69">
+        <f>'P&amp;L'!D14/'P&amp;L'!D5</f>
+        <v/>
+      </c>
+      <c r="E8" s="69">
+        <f>'P&amp;L'!E14/'P&amp;L'!E5</f>
+        <v/>
+      </c>
+      <c r="F8" s="69">
+        <f>'P&amp;L'!F14/'P&amp;L'!F5</f>
+        <v/>
+      </c>
+      <c r="G8" s="70">
+        <f>AVERAGE(B8:F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="70">
+        <f>G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="70">
+        <f>G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="70">
+        <f>G8</f>
+        <v/>
+      </c>
+      <c r="K8" s="70">
+        <f>G8</f>
+        <v/>
+      </c>
+      <c r="L8" s="71">
+        <f>G8</f>
+        <v/>
+      </c>
+      <c r="M8" s="72" t="inlineStr">
+        <is>
+          <t>Historical linked from P&amp;L.  Yr 1 = avg of historicals; Yrs 2-5 &amp; terminal = Yr 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>CapEx as % of Revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="69">
+        <f>-'Cash Flow'!B6/'P&amp;L'!B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="69">
+        <f>-'Cash Flow'!C6/'P&amp;L'!C5</f>
+        <v/>
+      </c>
+      <c r="D9" s="69">
+        <f>-'Cash Flow'!D6/'P&amp;L'!D5</f>
+        <v/>
+      </c>
+      <c r="E9" s="69">
+        <f>-'Cash Flow'!E6/'P&amp;L'!E5</f>
+        <v/>
+      </c>
+      <c r="F9" s="69">
+        <f>-'Cash Flow'!F6/'P&amp;L'!F5</f>
+        <v/>
+      </c>
+      <c r="G9" s="70">
+        <f>AVERAGE(B9:F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="70">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="70">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="70">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="K9" s="70">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="L9" s="71">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="M9" s="72" t="inlineStr">
+        <is>
+          <t>Historical linked from Cash Flow.  Yr 1 = avg of historicals; Yrs 2-5 &amp; terminal = Yr 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>Change in NWC as % of Revenue</t>
+        </is>
+      </c>
+      <c r="B10" s="68" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="70">
-        <f>'P&amp;L'!C5/'P&amp;L'!B5-1</f>
-        <v/>
-      </c>
-      <c r="D7" s="70">
-        <f>'P&amp;L'!D5/'P&amp;L'!C5-1</f>
-        <v/>
-      </c>
-      <c r="E7" s="70">
-        <f>'P&amp;L'!E5/'P&amp;L'!D5-1</f>
-        <v/>
-      </c>
-      <c r="F7" s="70">
-        <f>'P&amp;L'!F5/'P&amp;L'!E5-1</f>
-        <v/>
-      </c>
-      <c r="G7" s="71" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H7" s="71" t="n">
-        <v>0.1488</v>
-      </c>
-      <c r="I7" s="71" t="n">
-        <v>0.1803</v>
-      </c>
-      <c r="J7" s="72">
-        <f>I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="72">
-        <f>I7</f>
-        <v/>
-      </c>
-      <c r="L7" s="73" t="n">
+      <c r="C10" s="69">
+        <f>(('Balance Sheet'!C9-'Balance Sheet'!C21)-('Balance Sheet'!B9-'Balance Sheet'!B21))/'P&amp;L'!C5</f>
+        <v/>
+      </c>
+      <c r="D10" s="69">
+        <f>(('Balance Sheet'!D9-'Balance Sheet'!D21)-('Balance Sheet'!C9-'Balance Sheet'!C21))/'P&amp;L'!D5</f>
+        <v/>
+      </c>
+      <c r="E10" s="69">
+        <f>(('Balance Sheet'!E9-'Balance Sheet'!E21)-('Balance Sheet'!D9-'Balance Sheet'!D21))/'P&amp;L'!E5</f>
+        <v/>
+      </c>
+      <c r="F10" s="69">
+        <f>(('Balance Sheet'!F9-'Balance Sheet'!F21)-('Balance Sheet'!E9-'Balance Sheet'!E21))/'P&amp;L'!F5</f>
+        <v/>
+      </c>
+      <c r="G10" s="70">
+        <f>MAX(-0.02,MIN(0.05,AVERAGE(C10:F10)))</f>
+        <v/>
+      </c>
+      <c r="H10" s="70">
+        <f>G10*4/5</f>
+        <v/>
+      </c>
+      <c r="I10" s="70">
+        <f>G10*3/5</f>
+        <v/>
+      </c>
+      <c r="J10" s="70">
+        <f>G10*2/5</f>
+        <v/>
+      </c>
+      <c r="K10" s="70">
+        <f>G10*1/5</f>
+        <v/>
+      </c>
+      <c r="L10" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="72" t="inlineStr">
+        <is>
+          <t>Yr 1 = clamped avg of historicals [-2%, +5%]. Yrs 2-5 fade linearly to 0. Terminal = 0 (steady-state: NWC tracks revenue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>Effective Tax Rate</t>
+        </is>
+      </c>
+      <c r="B11" s="69">
+        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!B22/'P&amp;L'!B21)),0)</f>
+        <v/>
+      </c>
+      <c r="C11" s="69">
+        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!C22/'P&amp;L'!C21)),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="69">
+        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!D22/'P&amp;L'!D21)),0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="69">
+        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!E22/'P&amp;L'!E21)),0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="69">
+        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!F22/'P&amp;L'!F21)),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="70">
+        <f>AVERAGE(B11:F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="70">
+        <f>G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="70">
+        <f>G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="70">
+        <f>G11</f>
+        <v/>
+      </c>
+      <c r="K11" s="70">
+        <f>G11</f>
+        <v/>
+      </c>
+      <c r="L11" s="71">
+        <f>G11</f>
+        <v/>
+      </c>
+      <c r="M11" s="72" t="inlineStr">
+        <is>
+          <t>Historical linked from P&amp;L (tax / pretax income).  Forecast: avg of historicals, constant thereafter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="6" customHeight="1">
+      <c r="A12" s="42" t="n"/>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="42" t="n"/>
+      <c r="D12" s="42" t="n"/>
+      <c r="E12" s="42" t="n"/>
+      <c r="F12" s="42" t="n"/>
+      <c r="G12" s="42" t="n"/>
+      <c r="H12" s="42" t="n"/>
+      <c r="I12" s="42" t="n"/>
+      <c r="J12" s="42" t="n"/>
+      <c r="K12" s="42" t="n"/>
+      <c r="L12" s="42" t="n"/>
+      <c r="M12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>SECTION 2 — REVENUE &amp; EBITDA  ($mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="73" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="74">
+        <f>'P&amp;L'!B5</f>
+        <v/>
+      </c>
+      <c r="C14" s="74">
+        <f>'P&amp;L'!C5</f>
+        <v/>
+      </c>
+      <c r="D14" s="74">
+        <f>'P&amp;L'!D5</f>
+        <v/>
+      </c>
+      <c r="E14" s="74">
+        <f>'P&amp;L'!E5</f>
+        <v/>
+      </c>
+      <c r="F14" s="74">
+        <f>'P&amp;L'!F5</f>
+        <v/>
+      </c>
+      <c r="G14" s="75">
+        <f>F14*(1+G6)</f>
+        <v/>
+      </c>
+      <c r="H14" s="75">
+        <f>G14*(1+H6)</f>
+        <v/>
+      </c>
+      <c r="I14" s="75">
+        <f>H14*(1+I6)</f>
+        <v/>
+      </c>
+      <c r="J14" s="75">
+        <f>I14*(1+J6)</f>
+        <v/>
+      </c>
+      <c r="K14" s="75">
+        <f>J14*(1+K6)</f>
+        <v/>
+      </c>
+      <c r="L14" s="76">
+        <f>K14*(1+L6)</f>
+        <v/>
+      </c>
+      <c r="M14" s="77" t="inlineStr">
+        <is>
+          <t>FMP consensus years: analyst revenue average ($mm).  Range: Low–High shown below.  User years: prior × (1+growth).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Analyst Range:  Low — High  ($mm)</t>
+        </is>
+      </c>
+      <c r="G15" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="77" t="inlineStr">
+        <is>
+          <t>Sell-side analyst low / high revenue estimates for consensus years</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Number of Analysts</t>
+        </is>
+      </c>
+      <c r="G16" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="77" t="inlineStr">
+        <is>
+          <t>Red &lt; 5 analysts — treat estimate with caution.  Orange &lt; 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  YoY Revenue Growth %</t>
+        </is>
+      </c>
+      <c r="B17" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="82">
+        <f>IFERROR(C14/B14-1,"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="82">
+        <f>IFERROR(D14/C14-1,"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="82">
+        <f>IFERROR(E14/D14-1,"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="82">
+        <f>IFERROR(F14/E14-1,"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="83">
+        <f>IFERROR(G14/F14-1,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="83">
+        <f>IFERROR(H14/G14-1,"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="83">
+        <f>IFERROR(I14/H14-1,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="83">
+        <f>IFERROR(J14/I14-1,"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="83">
+        <f>IFERROR(K14/J14-1,"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="84">
+        <f>L6</f>
+        <v/>
+      </c>
+      <c r="M17" s="77">
+        <f> this year / prior year − 1  (formula cross-check on assumptions)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="6" customHeight="1">
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="42" t="n"/>
+      <c r="D18" s="42" t="n"/>
+      <c r="E18" s="42" t="n"/>
+      <c r="F18" s="42" t="n"/>
+      <c r="G18" s="42" t="n"/>
+      <c r="H18" s="42" t="n"/>
+      <c r="I18" s="42" t="n"/>
+      <c r="J18" s="42" t="n"/>
+      <c r="K18" s="42" t="n"/>
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="73" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B19" s="74">
+        <f>'P&amp;L'!B12</f>
+        <v/>
+      </c>
+      <c r="C19" s="74">
+        <f>'P&amp;L'!C12</f>
+        <v/>
+      </c>
+      <c r="D19" s="74">
+        <f>'P&amp;L'!D12</f>
+        <v/>
+      </c>
+      <c r="E19" s="74">
+        <f>'P&amp;L'!E12</f>
+        <v/>
+      </c>
+      <c r="F19" s="74">
+        <f>'P&amp;L'!F12</f>
+        <v/>
+      </c>
+      <c r="G19" s="75">
+        <f>G14*G7</f>
+        <v/>
+      </c>
+      <c r="H19" s="75">
+        <f>H14*H7</f>
+        <v/>
+      </c>
+      <c r="I19" s="75">
+        <f>I14*I7</f>
+        <v/>
+      </c>
+      <c r="J19" s="75">
+        <f>J14*J7</f>
+        <v/>
+      </c>
+      <c r="K19" s="75">
+        <f>K14*K7</f>
+        <v/>
+      </c>
+      <c r="L19" s="76">
+        <f>L14*L7</f>
+        <v/>
+      </c>
+      <c r="M19" s="77" t="inlineStr">
+        <is>
+          <t>FMP consensus years: analyst EBITDA average.  User years: Revenue × EBITDA margin assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Analyst Range:  Low — High  ($mm)</t>
+        </is>
+      </c>
+      <c r="G20" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="77" t="inlineStr">
+        <is>
+          <t>Sell-side analyst low / high EBITDA estimates for consensus years</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBITDA Margin %</t>
+        </is>
+      </c>
+      <c r="B21" s="82">
+        <f>IFERROR(B19/B14,"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="82">
+        <f>IFERROR(C19/C14,"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="82">
+        <f>IFERROR(D19/D14,"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="82">
+        <f>IFERROR(E19/E14,"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="82">
+        <f>IFERROR(F19/F14,"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="83">
+        <f>IFERROR(G19/G14,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="83">
+        <f>IFERROR(H19/H14,"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="83">
+        <f>IFERROR(I19/I14,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="83">
+        <f>IFERROR(J19/J14,"")</f>
+        <v/>
+      </c>
+      <c r="K21" s="83">
+        <f>IFERROR(K19/K14,"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="84">
+        <f>IFERROR(L19/L14,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="77">
+        <f> EBITDA / Revenue  (formula — cross-check on margin assumption)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="6" customHeight="1">
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="42" t="n"/>
+      <c r="I22" s="42" t="n"/>
+      <c r="J22" s="42" t="n"/>
+      <c r="K22" s="42" t="n"/>
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>SECTION 3 — UNLEVERED FREE CASH FLOW BUILD  ($mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: D&amp;A</t>
+        </is>
+      </c>
+      <c r="B24" s="74">
+        <f>-'P&amp;L'!B14</f>
+        <v/>
+      </c>
+      <c r="C24" s="74">
+        <f>-'P&amp;L'!C14</f>
+        <v/>
+      </c>
+      <c r="D24" s="74">
+        <f>-'P&amp;L'!D14</f>
+        <v/>
+      </c>
+      <c r="E24" s="74">
+        <f>-'P&amp;L'!E14</f>
+        <v/>
+      </c>
+      <c r="F24" s="74">
+        <f>-'P&amp;L'!F14</f>
+        <v/>
+      </c>
+      <c r="G24" s="75">
+        <f>-G14*G8</f>
+        <v/>
+      </c>
+      <c r="H24" s="75">
+        <f>-H14*H8</f>
+        <v/>
+      </c>
+      <c r="I24" s="75">
+        <f>-I14*I8</f>
+        <v/>
+      </c>
+      <c r="J24" s="75">
+        <f>-J14*J8</f>
+        <v/>
+      </c>
+      <c r="K24" s="75">
+        <f>-K14*K8</f>
+        <v/>
+      </c>
+      <c r="L24" s="76">
+        <f>-L14*L8</f>
+        <v/>
+      </c>
+      <c r="M24" s="77">
+        <f> Revenue × D&amp;A % assumption  (negative = P&amp;L charge)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="63" t="inlineStr">
+        <is>
+          <t>EBIT  (Operating Profit)</t>
+        </is>
+      </c>
+      <c r="B25" s="86">
+        <f>B19+B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="86">
+        <f>C19+C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="86">
+        <f>D19+D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="86">
+        <f>E19+E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="86">
+        <f>F19+F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="87">
+        <f>G19+G24</f>
+        <v/>
+      </c>
+      <c r="H25" s="87">
+        <f>H19+H24</f>
+        <v/>
+      </c>
+      <c r="I25" s="87">
+        <f>I19+I24</f>
+        <v/>
+      </c>
+      <c r="J25" s="87">
+        <f>J19+J24</f>
+        <v/>
+      </c>
+      <c r="K25" s="87">
+        <f>K19+K24</f>
+        <v/>
+      </c>
+      <c r="L25" s="87">
+        <f>L19+L24</f>
+        <v/>
+      </c>
+      <c r="M25" s="77">
+        <f> EBITDA + D&amp;A  (GAAP operating income, EBIT)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: Tax on EBIT  (unlevered)</t>
+        </is>
+      </c>
+      <c r="B26" s="88">
+        <f>-B25*B11</f>
+        <v/>
+      </c>
+      <c r="C26" s="88">
+        <f>-C25*C11</f>
+        <v/>
+      </c>
+      <c r="D26" s="88">
+        <f>-D25*D11</f>
+        <v/>
+      </c>
+      <c r="E26" s="88">
+        <f>-E25*E11</f>
+        <v/>
+      </c>
+      <c r="F26" s="88">
+        <f>-F25*F11</f>
+        <v/>
+      </c>
+      <c r="G26" s="89">
+        <f>-G25*G11</f>
+        <v/>
+      </c>
+      <c r="H26" s="89">
+        <f>-H25*H11</f>
+        <v/>
+      </c>
+      <c r="I26" s="89">
+        <f>-I25*I11</f>
+        <v/>
+      </c>
+      <c r="J26" s="89">
+        <f>-J25*J11</f>
+        <v/>
+      </c>
+      <c r="K26" s="89">
+        <f>-K25*K11</f>
+        <v/>
+      </c>
+      <c r="L26" s="89">
+        <f>-L25*L11</f>
+        <v/>
+      </c>
+      <c r="M26" s="77">
+        <f> EBIT × tax rate  (no interest tax shield — UFCF is pre-debt)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="73" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="B27" s="86">
+        <f>B25+B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="86">
+        <f>C25+C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="86">
+        <f>D25+D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="86">
+        <f>E25+E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="86">
+        <f>F25+F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="90">
+        <f>G25+G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="90">
+        <f>H25+H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="90">
+        <f>I25+I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="90">
+        <f>J25+J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="90">
+        <f>K25+K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="90">
+        <f>L25+L26</f>
+        <v/>
+      </c>
+      <c r="M27" s="77">
+        <f> EBIT × (1 − tax rate)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (+) D&amp;A add-back  (non-cash)</t>
+        </is>
+      </c>
+      <c r="B28" s="88">
+        <f>-B24</f>
+        <v/>
+      </c>
+      <c r="C28" s="88">
+        <f>-C24</f>
+        <v/>
+      </c>
+      <c r="D28" s="88">
+        <f>-D24</f>
+        <v/>
+      </c>
+      <c r="E28" s="88">
+        <f>-E24</f>
+        <v/>
+      </c>
+      <c r="F28" s="88">
+        <f>-F24</f>
+        <v/>
+      </c>
+      <c r="G28" s="89">
+        <f>-G24</f>
+        <v/>
+      </c>
+      <c r="H28" s="89">
+        <f>-H24</f>
+        <v/>
+      </c>
+      <c r="I28" s="89">
+        <f>-I24</f>
+        <v/>
+      </c>
+      <c r="J28" s="89">
+        <f>-J24</f>
+        <v/>
+      </c>
+      <c r="K28" s="89">
+        <f>-K24</f>
+        <v/>
+      </c>
+      <c r="L28" s="89">
+        <f>-L24</f>
+        <v/>
+      </c>
+      <c r="M28" s="77">
+        <f> D&amp;A added back (non-cash charge — converts NOPAT to cash basis)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (−) Capital Expenditures</t>
+        </is>
+      </c>
+      <c r="B29" s="74">
+        <f>'Cash Flow'!B6</f>
+        <v/>
+      </c>
+      <c r="C29" s="74">
+        <f>'Cash Flow'!C6</f>
+        <v/>
+      </c>
+      <c r="D29" s="74">
+        <f>'Cash Flow'!D6</f>
+        <v/>
+      </c>
+      <c r="E29" s="74">
+        <f>'Cash Flow'!E6</f>
+        <v/>
+      </c>
+      <c r="F29" s="74">
+        <f>'Cash Flow'!F6</f>
+        <v/>
+      </c>
+      <c r="G29" s="89">
+        <f>-G14*G9</f>
+        <v/>
+      </c>
+      <c r="H29" s="89">
+        <f>-H14*H9</f>
+        <v/>
+      </c>
+      <c r="I29" s="89">
+        <f>-I14*I9</f>
+        <v/>
+      </c>
+      <c r="J29" s="89">
+        <f>-J14*J9</f>
+        <v/>
+      </c>
+      <c r="K29" s="89">
+        <f>-K14*K9</f>
+        <v/>
+      </c>
+      <c r="L29" s="89">
+        <f>-L14*L9</f>
+        <v/>
+      </c>
+      <c r="M29" s="77">
+        <f> Revenue × CapEx % assumption  (negative = cash outflow)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (−) Increase in Net Working Capital</t>
+        </is>
+      </c>
+      <c r="B30" s="88" t="n"/>
+      <c r="C30" s="88">
+        <f>-(('Balance Sheet'!C9-'Balance Sheet'!C21)-('Balance Sheet'!B9-'Balance Sheet'!B21))</f>
+        <v/>
+      </c>
+      <c r="D30" s="88">
+        <f>-(('Balance Sheet'!D9-'Balance Sheet'!D21)-('Balance Sheet'!C9-'Balance Sheet'!C21))</f>
+        <v/>
+      </c>
+      <c r="E30" s="88">
+        <f>-(('Balance Sheet'!E9-'Balance Sheet'!E21)-('Balance Sheet'!D9-'Balance Sheet'!D21))</f>
+        <v/>
+      </c>
+      <c r="F30" s="88">
+        <f>-(('Balance Sheet'!F9-'Balance Sheet'!F21)-('Balance Sheet'!E9-'Balance Sheet'!E21))</f>
+        <v/>
+      </c>
+      <c r="G30" s="89">
+        <f>-G14*G10</f>
+        <v/>
+      </c>
+      <c r="H30" s="89">
+        <f>-H14*H10</f>
+        <v/>
+      </c>
+      <c r="I30" s="89">
+        <f>-I14*I10</f>
+        <v/>
+      </c>
+      <c r="J30" s="89">
+        <f>-J14*J10</f>
+        <v/>
+      </c>
+      <c r="K30" s="89">
+        <f>-K14*K10</f>
+        <v/>
+      </c>
+      <c r="L30" s="89">
+        <f>-L14*L10</f>
+        <v/>
+      </c>
+      <c r="M30" s="77">
+        <f> −Revenue × NWC%  (positive NWC% → cash outflow, reduces UFCF)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="73" t="inlineStr">
+        <is>
+          <t>UNLEVERED FREE CASH FLOW  (UFCF)</t>
+        </is>
+      </c>
+      <c r="B31" s="86">
+        <f>B27+B28+B29+B30</f>
+        <v/>
+      </c>
+      <c r="C31" s="86">
+        <f>C27+C28+C29+C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="86">
+        <f>D27+D28+D29+D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="86">
+        <f>E27+E28+E29+E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="86">
+        <f>F27+F28+F29+F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="90">
+        <f>G27+G28+G29+G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="90">
+        <f>H27+H28+H29+H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="90">
+        <f>I27+I28+I29+I30</f>
+        <v/>
+      </c>
+      <c r="J31" s="90">
+        <f>J27+J28+J29+J30</f>
+        <v/>
+      </c>
+      <c r="K31" s="90">
+        <f>K27+K28+K29+K30</f>
+        <v/>
+      </c>
+      <c r="L31" s="90">
+        <f>L27+L28+L29+L30</f>
+        <v/>
+      </c>
+      <c r="M31" s="77">
+        <f> NOPAT + D&amp;A − CapEx − ΔNWC  (pre-debt, pre-interest free cash flow)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  UFCF Margin %</t>
+        </is>
+      </c>
+      <c r="B32" s="82">
+        <f>B31/B14</f>
+        <v/>
+      </c>
+      <c r="C32" s="82">
+        <f>C31/C14</f>
+        <v/>
+      </c>
+      <c r="D32" s="82">
+        <f>D31/D14</f>
+        <v/>
+      </c>
+      <c r="E32" s="82">
+        <f>E31/E14</f>
+        <v/>
+      </c>
+      <c r="F32" s="82">
+        <f>F31/F14</f>
+        <v/>
+      </c>
+      <c r="G32" s="91">
+        <f>IFERROR(G31/G14,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="91">
+        <f>IFERROR(H31/H14,"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="91">
+        <f>IFERROR(I31/I14,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="91">
+        <f>IFERROR(J31/J14,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="91">
+        <f>IFERROR(K31/K14,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="91">
+        <f>IFERROR(L31/L14,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="77" t="inlineStr">
+        <is>
+          <t>Sense check — should approximate EBITDA margin less capex intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="6" customHeight="1">
+      <c r="A33" s="42" t="n"/>
+      <c r="B33" s="42" t="n"/>
+      <c r="C33" s="42" t="n"/>
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="42" t="n"/>
+      <c r="G33" s="42" t="n"/>
+      <c r="H33" s="42" t="n"/>
+      <c r="I33" s="42" t="n"/>
+      <c r="J33" s="42" t="n"/>
+      <c r="K33" s="42" t="n"/>
+      <c r="L33" s="42" t="n"/>
+      <c r="M33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>SECTION 4 — TERMINAL VALUE  ($mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="67" t="inlineStr">
+        <is>
+          <t>WACC  (from WACC tab)</t>
+        </is>
+      </c>
+      <c r="B35" s="92">
+        <f>WACC!B45</f>
+        <v/>
+      </c>
+      <c r="C35" s="93" t="n"/>
+      <c r="D35" s="93" t="n"/>
+      <c r="E35" s="93" t="n"/>
+      <c r="F35" s="93" t="n"/>
+      <c r="G35" s="93" t="n"/>
+      <c r="H35" s="93" t="n"/>
+      <c r="I35" s="93" t="n"/>
+      <c r="J35" s="93" t="n"/>
+      <c r="K35" s="93" t="n"/>
+      <c r="L35" s="93" t="n"/>
+      <c r="M35" s="72" t="inlineStr">
+        <is>
+          <t>Auto-linked from WACC tab selected output.  Override manually if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="67" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate  (g)</t>
+        </is>
+      </c>
+      <c r="B36" s="94" t="n">
         <v>0.03</v>
       </c>
-      <c r="M7" s="74" t="inlineStr">
-        <is>
-          <t>Yrs 1-3: FMP analyst consensus implied growth (back-calc from rev estimates).  Yrs 4-5: formula = Yr 3 growth.  Terminal = long-run growth (2-4%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="68" t="inlineStr">
-        <is>
-          <t>EBITDA Margin %</t>
-        </is>
-      </c>
-      <c r="B8" s="70">
-        <f>'P&amp;L'!B12/'P&amp;L'!B5</f>
-        <v/>
-      </c>
-      <c r="C8" s="70">
-        <f>'P&amp;L'!C12/'P&amp;L'!C5</f>
-        <v/>
-      </c>
-      <c r="D8" s="70">
-        <f>'P&amp;L'!D12/'P&amp;L'!D5</f>
-        <v/>
-      </c>
-      <c r="E8" s="70">
-        <f>'P&amp;L'!E12/'P&amp;L'!E5</f>
-        <v/>
-      </c>
-      <c r="F8" s="70">
-        <f>'P&amp;L'!F12/'P&amp;L'!F5</f>
-        <v/>
-      </c>
-      <c r="G8" s="71" t="n">
-        <v>0.1646</v>
-      </c>
-      <c r="H8" s="71" t="n">
-        <v>0.1646</v>
-      </c>
-      <c r="I8" s="71" t="n">
-        <v>0.1646</v>
-      </c>
-      <c r="J8" s="72">
-        <f>I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="72">
-        <f>I8</f>
-        <v/>
-      </c>
-      <c r="L8" s="73" t="n">
-        <v>0.1241</v>
-      </c>
-      <c r="M8" s="74" t="inlineStr">
-        <is>
-          <t>Yrs 1-3: FMP analyst consensus margin.  Yrs 4-5: = Yr 3 margin.  Terminal: long-run normalised EBITDA margin (user input).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="68" t="inlineStr">
-        <is>
-          <t>D&amp;A as % of Revenue</t>
-        </is>
-      </c>
-      <c r="B9" s="70">
-        <f>'P&amp;L'!B14/'P&amp;L'!B5</f>
-        <v/>
-      </c>
-      <c r="C9" s="70">
-        <f>'P&amp;L'!C14/'P&amp;L'!C5</f>
-        <v/>
-      </c>
-      <c r="D9" s="70">
-        <f>'P&amp;L'!D14/'P&amp;L'!D5</f>
-        <v/>
-      </c>
-      <c r="E9" s="70">
-        <f>'P&amp;L'!E14/'P&amp;L'!E5</f>
-        <v/>
-      </c>
-      <c r="F9" s="70">
-        <f>'P&amp;L'!F14/'P&amp;L'!F5</f>
-        <v/>
-      </c>
-      <c r="G9" s="72">
-        <f>AVERAGE(B9:F9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="72">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="72">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="J9" s="72">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="K9" s="72">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="L9" s="73">
-        <f>G9</f>
-        <v/>
-      </c>
-      <c r="M9" s="74" t="inlineStr">
-        <is>
-          <t>Historical linked from P&amp;L.  Yr 1 = avg of historicals; Yrs 2-5 &amp; terminal = Yr 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
-        <is>
-          <t>CapEx as % of Revenue</t>
-        </is>
-      </c>
-      <c r="B10" s="70">
-        <f>-'Cash Flow'!B6/'P&amp;L'!B5</f>
-        <v/>
-      </c>
-      <c r="C10" s="70">
-        <f>-'Cash Flow'!C6/'P&amp;L'!C5</f>
-        <v/>
-      </c>
-      <c r="D10" s="70">
-        <f>-'Cash Flow'!D6/'P&amp;L'!D5</f>
-        <v/>
-      </c>
-      <c r="E10" s="70">
-        <f>-'Cash Flow'!E6/'P&amp;L'!E5</f>
-        <v/>
-      </c>
-      <c r="F10" s="70">
-        <f>-'Cash Flow'!F6/'P&amp;L'!F5</f>
-        <v/>
-      </c>
-      <c r="G10" s="72">
-        <f>AVERAGE(B10:F10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="72">
-        <f>G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="72">
-        <f>G10</f>
-        <v/>
-      </c>
-      <c r="J10" s="72">
-        <f>G10</f>
-        <v/>
-      </c>
-      <c r="K10" s="72">
-        <f>G10</f>
-        <v/>
-      </c>
-      <c r="L10" s="73">
-        <f>G10</f>
-        <v/>
-      </c>
-      <c r="M10" s="74" t="inlineStr">
-        <is>
-          <t>Historical linked from Cash Flow.  Yr 1 = avg of historicals; Yrs 2-5 &amp; terminal = Yr 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="68" t="inlineStr">
-        <is>
-          <t>Change in NWC as % of Revenue</t>
-        </is>
-      </c>
-      <c r="B11" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="70">
-        <f>(('Balance Sheet'!C9-'Balance Sheet'!C21)-('Balance Sheet'!B9-'Balance Sheet'!B21))/'P&amp;L'!C5</f>
-        <v/>
-      </c>
-      <c r="D11" s="70">
-        <f>(('Balance Sheet'!D9-'Balance Sheet'!D21)-('Balance Sheet'!C9-'Balance Sheet'!C21))/'P&amp;L'!D5</f>
-        <v/>
-      </c>
-      <c r="E11" s="70">
-        <f>(('Balance Sheet'!E9-'Balance Sheet'!E21)-('Balance Sheet'!D9-'Balance Sheet'!D21))/'P&amp;L'!E5</f>
-        <v/>
-      </c>
-      <c r="F11" s="70">
-        <f>(('Balance Sheet'!F9-'Balance Sheet'!F21)-('Balance Sheet'!E9-'Balance Sheet'!E21))/'P&amp;L'!F5</f>
-        <v/>
-      </c>
-      <c r="G11" s="72">
-        <f>MAX(-0.02,MIN(0.05,AVERAGE(C11:F11)))</f>
-        <v/>
-      </c>
-      <c r="H11" s="72">
-        <f>G11*4/5</f>
-        <v/>
-      </c>
-      <c r="I11" s="72">
-        <f>G11*3/5</f>
-        <v/>
-      </c>
-      <c r="J11" s="72">
-        <f>G11*2/5</f>
-        <v/>
-      </c>
-      <c r="K11" s="72">
-        <f>G11*1/5</f>
-        <v/>
-      </c>
-      <c r="L11" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="74" t="inlineStr">
-        <is>
-          <t>Yr 1 = clamped avg of historicals [-2%, +5%]. Yrs 2-5 fade linearly to 0. Terminal = 0 (steady-state: NWC tracks revenue).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="68" t="inlineStr">
-        <is>
-          <t>Effective Tax Rate</t>
-        </is>
-      </c>
-      <c r="B12" s="70">
-        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!B22/'P&amp;L'!B21)),0)</f>
-        <v/>
-      </c>
-      <c r="C12" s="70">
-        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!C22/'P&amp;L'!C21)),0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="70">
-        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!D22/'P&amp;L'!D21)),0)</f>
-        <v/>
-      </c>
-      <c r="E12" s="70">
-        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!E22/'P&amp;L'!E21)),0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="70">
-        <f>IFERROR(MAX(0,MIN(0.5,'P&amp;L'!F22/'P&amp;L'!F21)),0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="72">
-        <f>AVERAGE(B12:F12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="72">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="72">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="J12" s="72">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="K12" s="72">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="L12" s="73">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="M12" s="74" t="inlineStr">
-        <is>
-          <t>Historical linked from P&amp;L (tax / pretax income).  Forecast: avg of historicals, constant thereafter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="6" customHeight="1">
-      <c r="A13" s="42" t="n"/>
-      <c r="B13" s="42" t="n"/>
-      <c r="C13" s="42" t="n"/>
-      <c r="D13" s="42" t="n"/>
-      <c r="E13" s="42" t="n"/>
-      <c r="F13" s="42" t="n"/>
-      <c r="G13" s="42" t="n"/>
-      <c r="H13" s="42" t="n"/>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>SECTION 2 — REVENUE &amp; EBITDA  ($mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="75" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B15" s="76">
-        <f>'P&amp;L'!B5</f>
-        <v/>
-      </c>
-      <c r="C15" s="76">
-        <f>'P&amp;L'!C5</f>
-        <v/>
-      </c>
-      <c r="D15" s="76">
-        <f>'P&amp;L'!D5</f>
-        <v/>
-      </c>
-      <c r="E15" s="76">
-        <f>'P&amp;L'!E5</f>
-        <v/>
-      </c>
-      <c r="F15" s="76">
-        <f>'P&amp;L'!F5</f>
-        <v/>
-      </c>
-      <c r="G15" s="77" t="n">
-        <v>102413</v>
-      </c>
-      <c r="H15" s="77" t="n">
-        <v>117657</v>
-      </c>
-      <c r="I15" s="77" t="n">
-        <v>138867.5</v>
-      </c>
-      <c r="J15" s="78">
-        <f>I15*(1+J7)</f>
-        <v/>
-      </c>
-      <c r="K15" s="78">
-        <f>J15*(1+K7)</f>
-        <v/>
-      </c>
-      <c r="L15" s="79">
-        <f>K15*(1+L7)</f>
-        <v/>
-      </c>
-      <c r="M15" s="80" t="inlineStr">
-        <is>
-          <t>FMP consensus years: analyst revenue average ($mm).  Range: Low–High shown below.  User years: prior × (1+growth).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Analyst Range:  Low — High  ($mm)</t>
-        </is>
-      </c>
-      <c r="G16" s="82" t="inlineStr">
-        <is>
-          <t>93,652 — 113,018</t>
-        </is>
-      </c>
-      <c r="H16" s="82" t="inlineStr">
-        <is>
-          <t>103,850 — 130,707</t>
-        </is>
-      </c>
-      <c r="I16" s="82" t="inlineStr">
-        <is>
-          <t>138,853 — 138,882</t>
-        </is>
-      </c>
-      <c r="J16" s="82" t="inlineStr">
-        <is>
-          <t>197,780 — 266,447</t>
-        </is>
-      </c>
-      <c r="K16" s="82" t="inlineStr">
-        <is>
-          <t>210,055 — 282,984</t>
-        </is>
-      </c>
-      <c r="L16" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="80" t="inlineStr">
-        <is>
-          <t>Sell-side analyst low / high revenue estimates for consensus years</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Number of Analysts</t>
-        </is>
-      </c>
-      <c r="G17" s="84" t="n">
-        <v>35</v>
-      </c>
-      <c r="H17" s="84" t="n">
-        <v>35</v>
-      </c>
-      <c r="I17" s="84" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" s="84" t="n">
-        <v>15</v>
-      </c>
-      <c r="K17" s="84" t="n">
-        <v>21</v>
-      </c>
-      <c r="L17" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="80" t="inlineStr">
-        <is>
-          <t>Red &lt; 5 analysts — treat estimate with caution.  Orange &lt; 10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  YoY Revenue Growth %</t>
-        </is>
-      </c>
-      <c r="B18" s="85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" s="86">
-        <f>IFERROR(C15/B15-1,"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="86">
-        <f>IFERROR(D15/C15-1,"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="86">
-        <f>IFERROR(E15/D15-1,"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="86">
-        <f>IFERROR(F15/E15-1,"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="87">
-        <f>IFERROR(G15/F15-1,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="87">
-        <f>IFERROR(H15/G15-1,"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="87">
-        <f>IFERROR(I15/H15-1,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="87">
-        <f>IFERROR(J15/I15-1,"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="87">
-        <f>IFERROR(K15/J15-1,"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="88">
-        <f>L7</f>
-        <v/>
-      </c>
-      <c r="M18" s="80">
-        <f> this year / prior year − 1  (formula cross-check on assumptions)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="6" customHeight="1">
-      <c r="A19" s="42" t="n"/>
-      <c r="B19" s="42" t="n"/>
-      <c r="C19" s="42" t="n"/>
-      <c r="D19" s="42" t="n"/>
-      <c r="E19" s="42" t="n"/>
-      <c r="F19" s="42" t="n"/>
-      <c r="G19" s="42" t="n"/>
-      <c r="H19" s="42" t="n"/>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="42" t="n"/>
-      <c r="K19" s="42" t="n"/>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="42" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="75" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B20" s="76">
-        <f>'P&amp;L'!B12</f>
-        <v/>
-      </c>
-      <c r="C20" s="76">
-        <f>'P&amp;L'!C12</f>
-        <v/>
-      </c>
-      <c r="D20" s="76">
-        <f>'P&amp;L'!D12</f>
-        <v/>
-      </c>
-      <c r="E20" s="76">
-        <f>'P&amp;L'!E12</f>
-        <v/>
-      </c>
-      <c r="F20" s="76">
-        <f>'P&amp;L'!F12</f>
-        <v/>
-      </c>
-      <c r="G20" s="77" t="n">
-        <v>16859</v>
-      </c>
-      <c r="H20" s="77" t="n">
-        <v>19368.4</v>
-      </c>
-      <c r="I20" s="77" t="n">
-        <v>22860</v>
-      </c>
-      <c r="J20" s="78">
-        <f>J15*J8</f>
-        <v/>
-      </c>
-      <c r="K20" s="78">
-        <f>K15*K8</f>
-        <v/>
-      </c>
-      <c r="L20" s="79">
-        <f>L15*L8</f>
-        <v/>
-      </c>
-      <c r="M20" s="80" t="inlineStr">
-        <is>
-          <t>FMP consensus years: analyst EBITDA average.  User years: Revenue × EBITDA margin assumption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Analyst Range:  Low — High  ($mm)</t>
-        </is>
-      </c>
-      <c r="G21" s="82" t="inlineStr">
-        <is>
-          <t>15,417 — 18,605</t>
-        </is>
-      </c>
-      <c r="H21" s="82" t="inlineStr">
-        <is>
-          <t>17,095 — 21,517</t>
-        </is>
-      </c>
-      <c r="I21" s="82" t="inlineStr">
-        <is>
-          <t>22,858 — 22,862</t>
-        </is>
-      </c>
-      <c r="J21" s="82" t="inlineStr">
-        <is>
-          <t>32,558 — 43,862</t>
-        </is>
-      </c>
-      <c r="K21" s="82" t="inlineStr">
-        <is>
-          <t>34,579 — 46,584</t>
-        </is>
-      </c>
-      <c r="L21" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="80" t="inlineStr">
-        <is>
-          <t>Sell-side analyst low / high EBITDA estimates for consensus years</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBITDA Margin %</t>
-        </is>
-      </c>
-      <c r="B22" s="86">
-        <f>IFERROR(B20/B15,"")</f>
-        <v/>
-      </c>
-      <c r="C22" s="86">
-        <f>IFERROR(C20/C15,"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="86">
-        <f>IFERROR(D20/D15,"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="86">
-        <f>IFERROR(E20/E15,"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="86">
-        <f>IFERROR(F20/F15,"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="87">
-        <f>IFERROR(G20/G15,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="87">
-        <f>IFERROR(H20/H15,"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="87">
-        <f>IFERROR(I20/I15,"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="87">
-        <f>IFERROR(J20/J15,"")</f>
-        <v/>
-      </c>
-      <c r="K22" s="87">
-        <f>IFERROR(K20/K15,"")</f>
-        <v/>
-      </c>
-      <c r="L22" s="88">
-        <f>IFERROR(L20/L15,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="80">
-        <f> EBITDA / Revenue  (formula — cross-check on margin assumption)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="6" customHeight="1">
-      <c r="A23" s="42" t="n"/>
-      <c r="B23" s="42" t="n"/>
-      <c r="C23" s="42" t="n"/>
-      <c r="D23" s="42" t="n"/>
-      <c r="E23" s="42" t="n"/>
-      <c r="F23" s="42" t="n"/>
-      <c r="G23" s="42" t="n"/>
-      <c r="H23" s="42" t="n"/>
-      <c r="I23" s="42" t="n"/>
-      <c r="J23" s="42" t="n"/>
-      <c r="K23" s="42" t="n"/>
-      <c r="L23" s="42" t="n"/>
-      <c r="M23" s="42" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>SECTION 3 — UNLEVERED FREE CASH FLOW BUILD  ($mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Less: D&amp;A</t>
-        </is>
-      </c>
-      <c r="B25" s="76">
-        <f>-'P&amp;L'!B14</f>
-        <v/>
-      </c>
-      <c r="C25" s="76">
-        <f>-'P&amp;L'!C14</f>
-        <v/>
-      </c>
-      <c r="D25" s="76">
-        <f>-'P&amp;L'!D14</f>
-        <v/>
-      </c>
-      <c r="E25" s="76">
-        <f>-'P&amp;L'!E14</f>
-        <v/>
-      </c>
-      <c r="F25" s="76">
-        <f>-'P&amp;L'!F14</f>
-        <v/>
-      </c>
-      <c r="G25" s="90">
-        <f>-G15*G9</f>
-        <v/>
-      </c>
-      <c r="H25" s="90">
-        <f>-H15*H9</f>
-        <v/>
-      </c>
-      <c r="I25" s="90">
-        <f>-I15*I9</f>
-        <v/>
-      </c>
-      <c r="J25" s="90">
-        <f>-J15*J9</f>
-        <v/>
-      </c>
-      <c r="K25" s="90">
-        <f>-K15*K9</f>
-        <v/>
-      </c>
-      <c r="L25" s="79">
-        <f>-L15*L9</f>
-        <v/>
-      </c>
-      <c r="M25" s="80">
-        <f> Revenue × D&amp;A % assumption  (negative = P&amp;L charge)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="63" t="inlineStr">
-        <is>
-          <t>EBIT  (Operating Profit)</t>
-        </is>
-      </c>
-      <c r="B26" s="91">
-        <f>B20+B25</f>
-        <v/>
-      </c>
-      <c r="C26" s="91">
-        <f>C20+C25</f>
-        <v/>
-      </c>
-      <c r="D26" s="91">
-        <f>D20+D25</f>
-        <v/>
-      </c>
-      <c r="E26" s="91">
-        <f>E20+E25</f>
-        <v/>
-      </c>
-      <c r="F26" s="91">
-        <f>F20+F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="92">
-        <f>G20+G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="92">
-        <f>H20+H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="92">
-        <f>I20+I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="92">
-        <f>J20+J25</f>
-        <v/>
-      </c>
-      <c r="K26" s="92">
-        <f>K20+K25</f>
-        <v/>
-      </c>
-      <c r="L26" s="92">
-        <f>L20+L25</f>
-        <v/>
-      </c>
-      <c r="M26" s="80">
-        <f> EBITDA + D&amp;A  (GAAP operating income, EBIT)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Less: Tax on EBIT  (unlevered)</t>
-        </is>
-      </c>
-      <c r="B27" s="93">
-        <f>-B26*B12</f>
-        <v/>
-      </c>
-      <c r="C27" s="93">
-        <f>-C26*C12</f>
-        <v/>
-      </c>
-      <c r="D27" s="93">
-        <f>-D26*D12</f>
-        <v/>
-      </c>
-      <c r="E27" s="93">
-        <f>-E26*E12</f>
-        <v/>
-      </c>
-      <c r="F27" s="93">
-        <f>-F26*F12</f>
-        <v/>
-      </c>
-      <c r="G27" s="94">
-        <f>-G26*G12</f>
-        <v/>
-      </c>
-      <c r="H27" s="94">
-        <f>-H26*H12</f>
-        <v/>
-      </c>
-      <c r="I27" s="94">
-        <f>-I26*I12</f>
-        <v/>
-      </c>
-      <c r="J27" s="94">
-        <f>-J26*J12</f>
-        <v/>
-      </c>
-      <c r="K27" s="94">
-        <f>-K26*K12</f>
-        <v/>
-      </c>
-      <c r="L27" s="94">
-        <f>-L26*L12</f>
-        <v/>
-      </c>
-      <c r="M27" s="80">
-        <f> EBIT × tax rate  (no interest tax shield — UFCF is pre-debt)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="75" t="inlineStr">
-        <is>
-          <t>NOPAT</t>
-        </is>
-      </c>
-      <c r="B28" s="91">
-        <f>B26+B27</f>
-        <v/>
-      </c>
-      <c r="C28" s="91">
-        <f>C26+C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="91">
-        <f>D26+D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="91">
-        <f>E26+E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="91">
-        <f>F26+F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="95">
-        <f>G26+G27</f>
-        <v/>
-      </c>
-      <c r="H28" s="95">
-        <f>H26+H27</f>
-        <v/>
-      </c>
-      <c r="I28" s="95">
-        <f>I26+I27</f>
-        <v/>
-      </c>
-      <c r="J28" s="95">
-        <f>J26+J27</f>
-        <v/>
-      </c>
-      <c r="K28" s="95">
-        <f>K26+K27</f>
-        <v/>
-      </c>
-      <c r="L28" s="95">
-        <f>L26+L27</f>
-        <v/>
-      </c>
-      <c r="M28" s="80">
-        <f> EBIT × (1 − tax rate)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (+) D&amp;A add-back  (non-cash)</t>
-        </is>
-      </c>
-      <c r="B29" s="93">
-        <f>-B25</f>
-        <v/>
-      </c>
-      <c r="C29" s="93">
-        <f>-C25</f>
-        <v/>
-      </c>
-      <c r="D29" s="93">
-        <f>-D25</f>
-        <v/>
-      </c>
-      <c r="E29" s="93">
-        <f>-E25</f>
-        <v/>
-      </c>
-      <c r="F29" s="93">
-        <f>-F25</f>
-        <v/>
-      </c>
-      <c r="G29" s="94">
-        <f>-G25</f>
-        <v/>
-      </c>
-      <c r="H29" s="94">
-        <f>-H25</f>
-        <v/>
-      </c>
-      <c r="I29" s="94">
-        <f>-I25</f>
-        <v/>
-      </c>
-      <c r="J29" s="94">
-        <f>-J25</f>
-        <v/>
-      </c>
-      <c r="K29" s="94">
-        <f>-K25</f>
-        <v/>
-      </c>
-      <c r="L29" s="94">
-        <f>-L25</f>
-        <v/>
-      </c>
-      <c r="M29" s="80">
-        <f> D&amp;A added back (non-cash charge — converts NOPAT to cash basis)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (−) Capital Expenditures</t>
-        </is>
-      </c>
-      <c r="B30" s="76">
-        <f>'Cash Flow'!B6</f>
-        <v/>
-      </c>
-      <c r="C30" s="76">
-        <f>'Cash Flow'!C6</f>
-        <v/>
-      </c>
-      <c r="D30" s="76">
-        <f>'Cash Flow'!D6</f>
-        <v/>
-      </c>
-      <c r="E30" s="76">
-        <f>'Cash Flow'!E6</f>
-        <v/>
-      </c>
-      <c r="F30" s="76">
-        <f>'Cash Flow'!F6</f>
-        <v/>
-      </c>
-      <c r="G30" s="94">
-        <f>-G15*G10</f>
-        <v/>
-      </c>
-      <c r="H30" s="94">
-        <f>-H15*H10</f>
-        <v/>
-      </c>
-      <c r="I30" s="94">
-        <f>-I15*I10</f>
-        <v/>
-      </c>
-      <c r="J30" s="94">
-        <f>-J15*J10</f>
-        <v/>
-      </c>
-      <c r="K30" s="94">
-        <f>-K15*K10</f>
-        <v/>
-      </c>
-      <c r="L30" s="94">
-        <f>-L15*L10</f>
-        <v/>
-      </c>
-      <c r="M30" s="80">
-        <f> Revenue × CapEx % assumption  (negative = cash outflow)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (−) Increase in Net Working Capital</t>
-        </is>
-      </c>
-      <c r="B31" s="93" t="n"/>
-      <c r="C31" s="93">
-        <f>-(('Balance Sheet'!C9-'Balance Sheet'!C21)-('Balance Sheet'!B9-'Balance Sheet'!B21))</f>
-        <v/>
-      </c>
-      <c r="D31" s="93">
-        <f>-(('Balance Sheet'!D9-'Balance Sheet'!D21)-('Balance Sheet'!C9-'Balance Sheet'!C21))</f>
-        <v/>
-      </c>
-      <c r="E31" s="93">
-        <f>-(('Balance Sheet'!E9-'Balance Sheet'!E21)-('Balance Sheet'!D9-'Balance Sheet'!D21))</f>
-        <v/>
-      </c>
-      <c r="F31" s="93">
-        <f>-(('Balance Sheet'!F9-'Balance Sheet'!F21)-('Balance Sheet'!E9-'Balance Sheet'!E21))</f>
-        <v/>
-      </c>
-      <c r="G31" s="94">
-        <f>-G15*G11</f>
-        <v/>
-      </c>
-      <c r="H31" s="94">
-        <f>-H15*H11</f>
-        <v/>
-      </c>
-      <c r="I31" s="94">
-        <f>-I15*I11</f>
-        <v/>
-      </c>
-      <c r="J31" s="94">
-        <f>-J15*J11</f>
-        <v/>
-      </c>
-      <c r="K31" s="94">
-        <f>-K15*K11</f>
-        <v/>
-      </c>
-      <c r="L31" s="94">
-        <f>-L15*L11</f>
-        <v/>
-      </c>
-      <c r="M31" s="80">
-        <f> −Revenue × NWC%  (positive NWC% → cash outflow, reduces UFCF)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="75" t="inlineStr">
-        <is>
-          <t>UNLEVERED FREE CASH FLOW  (UFCF)</t>
-        </is>
-      </c>
-      <c r="B32" s="91">
-        <f>B28+B29+B30+B31</f>
-        <v/>
-      </c>
-      <c r="C32" s="91">
-        <f>C28+C29+C30+C31</f>
-        <v/>
-      </c>
-      <c r="D32" s="91">
-        <f>D28+D29+D30+D31</f>
-        <v/>
-      </c>
-      <c r="E32" s="91">
-        <f>E28+E29+E30+E31</f>
-        <v/>
-      </c>
-      <c r="F32" s="91">
-        <f>F28+F29+F30+F31</f>
-        <v/>
-      </c>
-      <c r="G32" s="95">
-        <f>G28+G29+G30+G31</f>
-        <v/>
-      </c>
-      <c r="H32" s="95">
-        <f>H28+H29+H30+H31</f>
-        <v/>
-      </c>
-      <c r="I32" s="95">
-        <f>I28+I29+I30+I31</f>
-        <v/>
-      </c>
-      <c r="J32" s="95">
-        <f>J28+J29+J30+J31</f>
-        <v/>
-      </c>
-      <c r="K32" s="95">
-        <f>K28+K29+K30+K31</f>
-        <v/>
-      </c>
-      <c r="L32" s="95">
-        <f>L28+L29+L30+L31</f>
-        <v/>
-      </c>
-      <c r="M32" s="80">
-        <f> NOPAT + D&amp;A − CapEx − ΔNWC  (pre-debt, pre-interest free cash flow)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  UFCF Margin %</t>
-        </is>
-      </c>
-      <c r="B33" s="86">
-        <f>B32/B15</f>
-        <v/>
-      </c>
-      <c r="C33" s="86">
-        <f>C32/C15</f>
-        <v/>
-      </c>
-      <c r="D33" s="86">
-        <f>D32/D15</f>
-        <v/>
-      </c>
-      <c r="E33" s="86">
-        <f>E32/E15</f>
-        <v/>
-      </c>
-      <c r="F33" s="86">
-        <f>F32/F15</f>
-        <v/>
-      </c>
-      <c r="G33" s="96">
-        <f>IFERROR(G32/G15,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="96">
-        <f>IFERROR(H32/H15,"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="96">
-        <f>IFERROR(I32/I15,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="96">
-        <f>IFERROR(J32/J15,"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="96">
-        <f>IFERROR(K32/K15,"")</f>
-        <v/>
-      </c>
-      <c r="L33" s="96">
-        <f>IFERROR(L32/L15,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="80" t="inlineStr">
-        <is>
-          <t>Sense check — should approximate EBITDA margin less capex intensity</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="6" customHeight="1">
-      <c r="A34" s="42" t="n"/>
-      <c r="B34" s="42" t="n"/>
-      <c r="C34" s="42" t="n"/>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="42" t="n"/>
-      <c r="G34" s="42" t="n"/>
-      <c r="H34" s="42" t="n"/>
-      <c r="I34" s="42" t="n"/>
-      <c r="J34" s="42" t="n"/>
-      <c r="K34" s="42" t="n"/>
-      <c r="L34" s="42" t="n"/>
-      <c r="M34" s="42" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>SECTION 4 — TERMINAL VALUE  ($mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="68" t="inlineStr">
-        <is>
-          <t>WACC  (from WACC tab)</t>
-        </is>
-      </c>
-      <c r="B36" s="97">
-        <f>WACC!B45</f>
-        <v/>
-      </c>
-      <c r="C36" s="98" t="n"/>
-      <c r="D36" s="98" t="n"/>
-      <c r="E36" s="98" t="n"/>
-      <c r="F36" s="98" t="n"/>
-      <c r="G36" s="98" t="n"/>
-      <c r="H36" s="98" t="n"/>
-      <c r="I36" s="98" t="n"/>
-      <c r="J36" s="98" t="n"/>
-      <c r="K36" s="98" t="n"/>
-      <c r="L36" s="98" t="n"/>
-      <c r="M36" s="74" t="inlineStr">
-        <is>
-          <t>Auto-linked from WACC tab selected output.  Override manually if needed.</t>
+      <c r="C36" s="93" t="n"/>
+      <c r="D36" s="93" t="n"/>
+      <c r="E36" s="93" t="n"/>
+      <c r="F36" s="93" t="n"/>
+      <c r="G36" s="93" t="n"/>
+      <c r="H36" s="93" t="n"/>
+      <c r="I36" s="93" t="n"/>
+      <c r="J36" s="93" t="n"/>
+      <c r="K36" s="93" t="n"/>
+      <c r="L36" s="93" t="n"/>
+      <c r="M36" s="72" t="inlineStr">
+        <is>
+          <t>Growth tier: MEDIUM (5.6% 3yr avg rev growth).  Bear 2.25% / Base 3.0% / Bull 3.75%.  Keep below WACC.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="68" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate  (g)</t>
-        </is>
-      </c>
-      <c r="B37" s="99" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C37" s="98" t="n"/>
-      <c r="D37" s="98" t="n"/>
-      <c r="E37" s="98" t="n"/>
-      <c r="F37" s="98" t="n"/>
-      <c r="G37" s="98" t="n"/>
-      <c r="H37" s="98" t="n"/>
-      <c r="I37" s="98" t="n"/>
-      <c r="J37" s="98" t="n"/>
-      <c r="K37" s="98" t="n"/>
-      <c r="L37" s="98" t="n"/>
-      <c r="M37" s="74" t="inlineStr">
-        <is>
-          <t>Growth tier: MEDIUM (5.6% 3yr avg rev growth).  Bear 2.25% / Base 3.0% / Bull 3.75%.  Keep below WACC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="68" t="inlineStr">
+      <c r="A37" s="67" t="inlineStr">
         <is>
           <t>Terminal EV/EBITDA Multiple  (exit multiple method)</t>
         </is>
       </c>
-      <c r="B38" s="100" t="n">
+      <c r="B37" s="95" t="n">
         <v>28</v>
       </c>
-      <c r="C38" s="98" t="n"/>
-      <c r="D38" s="98" t="n"/>
-      <c r="E38" s="98" t="n"/>
-      <c r="F38" s="98" t="n"/>
-      <c r="G38" s="98" t="n"/>
-      <c r="H38" s="98" t="n"/>
-      <c r="I38" s="98" t="n"/>
-      <c r="J38" s="98" t="n"/>
-      <c r="K38" s="98" t="n"/>
-      <c r="L38" s="98" t="n"/>
-      <c r="M38" s="74" t="inlineStr">
+      <c r="C37" s="93" t="n"/>
+      <c r="D37" s="93" t="n"/>
+      <c r="E37" s="93" t="n"/>
+      <c r="F37" s="93" t="n"/>
+      <c r="G37" s="93" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="93" t="n"/>
+      <c r="J37" s="93" t="n"/>
+      <c r="K37" s="93" t="n"/>
+      <c r="L37" s="93" t="n"/>
+      <c r="M37" s="72" t="inlineStr">
         <is>
           <t>Growth tier: MEDIUM (5.6% 3yr avg rev growth).  Bear 20x / Base 28x / Bull 32x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="6" customHeight="1">
-      <c r="A39" s="42" t="n"/>
-      <c r="B39" s="42" t="n"/>
-      <c r="C39" s="42" t="n"/>
-      <c r="D39" s="42" t="n"/>
-      <c r="E39" s="42" t="n"/>
-      <c r="F39" s="42" t="n"/>
-      <c r="G39" s="42" t="n"/>
-      <c r="H39" s="42" t="n"/>
-      <c r="I39" s="42" t="n"/>
-      <c r="J39" s="42" t="n"/>
-      <c r="K39" s="42" t="n"/>
-      <c r="L39" s="42" t="n"/>
-      <c r="M39" s="42" t="n"/>
+    <row r="38" ht="6" customHeight="1">
+      <c r="A38" s="42" t="n"/>
+      <c r="B38" s="42" t="n"/>
+      <c r="C38" s="42" t="n"/>
+      <c r="D38" s="42" t="n"/>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="42" t="n"/>
+      <c r="H38" s="42" t="n"/>
+      <c r="I38" s="42" t="n"/>
+      <c r="J38" s="42" t="n"/>
+      <c r="K38" s="42" t="n"/>
+      <c r="L38" s="42" t="n"/>
+      <c r="M38" s="42" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="96" t="inlineStr">
+        <is>
+          <t>Terminal Year UFCF  (grown by g)</t>
+        </is>
+      </c>
+      <c r="B39" s="97">
+        <f>L31</f>
+        <v/>
+      </c>
+      <c r="C39" s="98" t="n"/>
+      <c r="D39" s="98" t="n"/>
+      <c r="E39" s="98" t="n"/>
+      <c r="F39" s="98" t="n"/>
+      <c r="G39" s="98" t="n"/>
+      <c r="H39" s="98" t="n"/>
+      <c r="I39" s="98" t="n"/>
+      <c r="J39" s="98" t="n"/>
+      <c r="K39" s="98" t="n"/>
+      <c r="L39" s="98" t="n"/>
+      <c r="M39" s="77" t="inlineStr">
+        <is>
+          <t>Cross-ref from Section 3 — terminal year UFCF (already grown by g in assumptions)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="101" t="inlineStr">
-        <is>
-          <t>Terminal Year UFCF  (grown by g)</t>
-        </is>
-      </c>
-      <c r="B40" s="102">
-        <f>L32</f>
-        <v/>
-      </c>
-      <c r="C40" s="103" t="n"/>
-      <c r="D40" s="103" t="n"/>
-      <c r="E40" s="103" t="n"/>
-      <c r="F40" s="103" t="n"/>
-      <c r="G40" s="103" t="n"/>
-      <c r="H40" s="103" t="n"/>
-      <c r="I40" s="103" t="n"/>
-      <c r="J40" s="103" t="n"/>
-      <c r="K40" s="103" t="n"/>
-      <c r="L40" s="103" t="n"/>
-      <c r="M40" s="80" t="inlineStr">
-        <is>
-          <t>Cross-ref from Section 3 — terminal year UFCF (already grown by g in assumptions)</t>
+      <c r="A40" s="73" t="inlineStr">
+        <is>
+          <t>Terminal Value  [Gordon Growth:  UFCF / (WACC − g)]</t>
+        </is>
+      </c>
+      <c r="B40" s="90">
+        <f>B39/(B35-B36)</f>
+        <v/>
+      </c>
+      <c r="C40" s="99" t="n"/>
+      <c r="D40" s="99" t="n"/>
+      <c r="E40" s="99" t="n"/>
+      <c r="F40" s="99" t="n"/>
+      <c r="G40" s="99" t="n"/>
+      <c r="H40" s="99" t="n"/>
+      <c r="I40" s="99" t="n"/>
+      <c r="J40" s="99" t="n"/>
+      <c r="K40" s="99" t="n"/>
+      <c r="L40" s="99" t="n"/>
+      <c r="M40" s="77" t="inlineStr">
+        <is>
+          <t>Sensitive to g — always cross-check vs Exit Multiple below</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="75" t="inlineStr">
-        <is>
-          <t>Terminal Value  [Gordon Growth:  UFCF / (WACC − g)]</t>
-        </is>
-      </c>
-      <c r="B41" s="95">
-        <f>B40/(B36-B37)</f>
-        <v/>
-      </c>
-      <c r="C41" s="104" t="n"/>
-      <c r="D41" s="104" t="n"/>
-      <c r="E41" s="104" t="n"/>
-      <c r="F41" s="104" t="n"/>
-      <c r="G41" s="104" t="n"/>
-      <c r="H41" s="104" t="n"/>
-      <c r="I41" s="104" t="n"/>
-      <c r="J41" s="104" t="n"/>
-      <c r="K41" s="104" t="n"/>
-      <c r="L41" s="104" t="n"/>
-      <c r="M41" s="80" t="inlineStr">
-        <is>
-          <t>Sensitive to g — always cross-check vs Exit Multiple below</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="75" t="inlineStr">
+      <c r="A41" s="73" t="inlineStr">
         <is>
           <t>Terminal Value  [Exit Multiple:  Terminal EBITDA × Multiple]</t>
         </is>
       </c>
-      <c r="B42" s="95">
-        <f>L20*B38</f>
-        <v/>
-      </c>
-      <c r="C42" s="104" t="n"/>
-      <c r="D42" s="104" t="n"/>
-      <c r="E42" s="104" t="n"/>
-      <c r="F42" s="104" t="n"/>
-      <c r="G42" s="104" t="n"/>
-      <c r="H42" s="104" t="n"/>
-      <c r="I42" s="104" t="n"/>
-      <c r="J42" s="104" t="n"/>
-      <c r="K42" s="104" t="n"/>
-      <c r="L42" s="104" t="n"/>
-      <c r="M42" s="80" t="inlineStr">
+      <c r="B41" s="90">
+        <f>L19*B37</f>
+        <v/>
+      </c>
+      <c r="C41" s="99" t="n"/>
+      <c r="D41" s="99" t="n"/>
+      <c r="E41" s="99" t="n"/>
+      <c r="F41" s="99" t="n"/>
+      <c r="G41" s="99" t="n"/>
+      <c r="H41" s="99" t="n"/>
+      <c r="I41" s="99" t="n"/>
+      <c r="J41" s="99" t="n"/>
+      <c r="K41" s="99" t="n"/>
+      <c r="L41" s="99" t="n"/>
+      <c r="M41" s="77" t="inlineStr">
         <is>
           <t>Anchored to observable market multiples — less model-sensitive than Gordon Growth</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="6" customHeight="1">
-      <c r="A43" s="42" t="n"/>
-      <c r="B43" s="42" t="n"/>
-      <c r="C43" s="42" t="n"/>
-      <c r="D43" s="42" t="n"/>
-      <c r="E43" s="42" t="n"/>
-      <c r="F43" s="42" t="n"/>
-      <c r="G43" s="42" t="n"/>
-      <c r="H43" s="42" t="n"/>
-      <c r="I43" s="42" t="n"/>
-      <c r="J43" s="42" t="n"/>
-      <c r="K43" s="42" t="n"/>
-      <c r="L43" s="42" t="n"/>
-      <c r="M43" s="42" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
+    <row r="42" ht="6" customHeight="1">
+      <c r="A42" s="42" t="n"/>
+      <c r="B42" s="42" t="n"/>
+      <c r="C42" s="42" t="n"/>
+      <c r="D42" s="42" t="n"/>
+      <c r="E42" s="42" t="n"/>
+      <c r="F42" s="42" t="n"/>
+      <c r="G42" s="42" t="n"/>
+      <c r="H42" s="42" t="n"/>
+      <c r="I42" s="42" t="n"/>
+      <c r="J42" s="42" t="n"/>
+      <c r="K42" s="42" t="n"/>
+      <c r="L42" s="42" t="n"/>
+      <c r="M42" s="42" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>SECTION 5 — DISCOUNTING  &amp;  ENTERPRISE VALUE  ($mm)</t>
         </is>
       </c>
     </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="96" t="inlineStr">
+        <is>
+          <t>Discount Period  (mid-year convention)</t>
+        </is>
+      </c>
+      <c r="G44" s="100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H44" s="100" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I44" s="100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J44" s="100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K44" s="100" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L44" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="M44" s="77" t="inlineStr">
+        <is>
+          <t>Mid-year: 0.5, 1.5, 2.5...  assumes FCF received evenly through each year</t>
+        </is>
+      </c>
+    </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="101" t="inlineStr">
-        <is>
-          <t>Discount Period  (mid-year convention)</t>
-        </is>
-      </c>
-      <c r="G45" s="105" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H45" s="105" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I45" s="105" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J45" s="105" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K45" s="105" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L45" s="106" t="n">
-        <v>5</v>
-      </c>
-      <c r="M45" s="80" t="inlineStr">
-        <is>
-          <t>Mid-year: 0.5, 1.5, 2.5...  assumes FCF received evenly through each year</t>
-        </is>
+      <c r="A45" s="96" t="inlineStr">
+        <is>
+          <t>Discount Factor  =  1 / (1 + WACC) ^ period</t>
+        </is>
+      </c>
+      <c r="G45" s="102">
+        <f>1/(1+B35)^G44</f>
+        <v/>
+      </c>
+      <c r="H45" s="102">
+        <f>1/(1+B35)^H44</f>
+        <v/>
+      </c>
+      <c r="I45" s="102">
+        <f>1/(1+B35)^I44</f>
+        <v/>
+      </c>
+      <c r="J45" s="102">
+        <f>1/(1+B35)^J44</f>
+        <v/>
+      </c>
+      <c r="K45" s="102">
+        <f>1/(1+B35)^K44</f>
+        <v/>
+      </c>
+      <c r="L45" s="103">
+        <f>1/(1+B35)^L44</f>
+        <v/>
+      </c>
+      <c r="M45" s="77">
+        <f> 1 / (1 + WACC) ^ discount period</f>
+        <v/>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="101" t="inlineStr">
-        <is>
-          <t>Discount Factor  =  1 / (1 + WACC) ^ period</t>
-        </is>
-      </c>
-      <c r="G46" s="107">
-        <f>1/(1+B36)^G45</f>
-        <v/>
-      </c>
-      <c r="H46" s="107">
-        <f>1/(1+B36)^H45</f>
-        <v/>
-      </c>
-      <c r="I46" s="107">
-        <f>1/(1+B36)^I45</f>
-        <v/>
-      </c>
-      <c r="J46" s="107">
-        <f>1/(1+B36)^J45</f>
-        <v/>
-      </c>
-      <c r="K46" s="107">
-        <f>1/(1+B36)^K45</f>
-        <v/>
-      </c>
-      <c r="L46" s="108">
-        <f>1/(1+B36)^L45</f>
-        <v/>
-      </c>
-      <c r="M46" s="80">
-        <f> 1 / (1 + WACC) ^ discount period</f>
+      <c r="A46" s="73" t="inlineStr">
+        <is>
+          <t>PV of UFCF</t>
+        </is>
+      </c>
+      <c r="G46" s="90">
+        <f>G31*G45</f>
+        <v/>
+      </c>
+      <c r="H46" s="90">
+        <f>H31*H45</f>
+        <v/>
+      </c>
+      <c r="I46" s="90">
+        <f>I31*I45</f>
+        <v/>
+      </c>
+      <c r="J46" s="90">
+        <f>J31*J45</f>
+        <v/>
+      </c>
+      <c r="K46" s="90">
+        <f>K31*K45</f>
+        <v/>
+      </c>
+      <c r="L46" s="99" t="n"/>
+      <c r="M46" s="77">
+        <f> UFCF × discount factor</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="75" t="inlineStr">
-        <is>
-          <t>PV of UFCF</t>
-        </is>
-      </c>
-      <c r="G47" s="95">
-        <f>G32*G46</f>
-        <v/>
-      </c>
-      <c r="H47" s="95">
-        <f>H32*H46</f>
-        <v/>
-      </c>
-      <c r="I47" s="95">
-        <f>I32*I46</f>
-        <v/>
-      </c>
-      <c r="J47" s="95">
-        <f>J32*J46</f>
-        <v/>
-      </c>
-      <c r="K47" s="95">
-        <f>K32*K46</f>
-        <v/>
-      </c>
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>Sum of PV of FCFs  (explicit period)</t>
+        </is>
+      </c>
+      <c r="B47" s="87">
+        <f>G46+H46+I46+J46+K46</f>
+        <v/>
+      </c>
+      <c r="C47" s="104" t="n"/>
+      <c r="D47" s="104" t="n"/>
+      <c r="E47" s="104" t="n"/>
+      <c r="F47" s="104" t="n"/>
+      <c r="G47" s="104" t="n"/>
+      <c r="H47" s="104" t="n"/>
+      <c r="I47" s="104" t="n"/>
+      <c r="J47" s="104" t="n"/>
+      <c r="K47" s="104" t="n"/>
       <c r="L47" s="104" t="n"/>
-      <c r="M47" s="80">
-        <f> UFCF × discount factor</f>
-        <v/>
+      <c r="M47" s="77" t="inlineStr">
+        <is>
+          <t>Sum of 5 discounted annual FCFs</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="63" t="inlineStr">
         <is>
-          <t>Sum of PV of FCFs  (explicit period)</t>
-        </is>
-      </c>
-      <c r="B48" s="92">
-        <f>G47+H47+I47+J47+K47</f>
-        <v/>
-      </c>
-      <c r="C48" s="109" t="n"/>
-      <c r="D48" s="109" t="n"/>
-      <c r="E48" s="109" t="n"/>
-      <c r="F48" s="109" t="n"/>
-      <c r="G48" s="109" t="n"/>
-      <c r="H48" s="109" t="n"/>
-      <c r="I48" s="109" t="n"/>
-      <c r="J48" s="109" t="n"/>
-      <c r="K48" s="109" t="n"/>
-      <c r="L48" s="109" t="n"/>
-      <c r="M48" s="80" t="inlineStr">
-        <is>
-          <t>Sum of 5 discounted annual FCFs</t>
+          <t>PV of Terminal Value  [Gordon Growth]</t>
+        </is>
+      </c>
+      <c r="B48" s="87">
+        <f>B40*L45</f>
+        <v/>
+      </c>
+      <c r="C48" s="104" t="n"/>
+      <c r="D48" s="104" t="n"/>
+      <c r="E48" s="104" t="n"/>
+      <c r="F48" s="104" t="n"/>
+      <c r="G48" s="104" t="n"/>
+      <c r="H48" s="104" t="n"/>
+      <c r="I48" s="104" t="n"/>
+      <c r="J48" s="104" t="n"/>
+      <c r="K48" s="104" t="n"/>
+      <c r="L48" s="104" t="n"/>
+      <c r="M48" s="77" t="inlineStr">
+        <is>
+          <t>Terminal value × terminal-year discount factor</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="63" t="inlineStr">
         <is>
-          <t>PV of Terminal Value  [Gordon Growth]</t>
-        </is>
-      </c>
-      <c r="B49" s="92">
-        <f>B41*L46</f>
-        <v/>
-      </c>
-      <c r="C49" s="109" t="n"/>
-      <c r="D49" s="109" t="n"/>
-      <c r="E49" s="109" t="n"/>
-      <c r="F49" s="109" t="n"/>
-      <c r="G49" s="109" t="n"/>
-      <c r="H49" s="109" t="n"/>
-      <c r="I49" s="109" t="n"/>
-      <c r="J49" s="109" t="n"/>
-      <c r="K49" s="109" t="n"/>
-      <c r="L49" s="109" t="n"/>
-      <c r="M49" s="80" t="inlineStr">
+          <t>PV of Terminal Value  [Exit Multiple]</t>
+        </is>
+      </c>
+      <c r="B49" s="87">
+        <f>B41*L45</f>
+        <v/>
+      </c>
+      <c r="C49" s="104" t="n"/>
+      <c r="D49" s="104" t="n"/>
+      <c r="E49" s="104" t="n"/>
+      <c r="F49" s="104" t="n"/>
+      <c r="G49" s="104" t="n"/>
+      <c r="H49" s="104" t="n"/>
+      <c r="I49" s="104" t="n"/>
+      <c r="J49" s="104" t="n"/>
+      <c r="K49" s="104" t="n"/>
+      <c r="L49" s="104" t="n"/>
+      <c r="M49" s="77" t="inlineStr">
         <is>
           <t>Terminal value × terminal-year discount factor</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="63" t="inlineStr">
-        <is>
-          <t>PV of Terminal Value  [Exit Multiple]</t>
-        </is>
-      </c>
-      <c r="B50" s="92">
-        <f>B42*L46</f>
-        <v/>
-      </c>
-      <c r="C50" s="109" t="n"/>
-      <c r="D50" s="109" t="n"/>
-      <c r="E50" s="109" t="n"/>
-      <c r="F50" s="109" t="n"/>
-      <c r="G50" s="109" t="n"/>
-      <c r="H50" s="109" t="n"/>
-      <c r="I50" s="109" t="n"/>
-      <c r="J50" s="109" t="n"/>
-      <c r="K50" s="109" t="n"/>
-      <c r="L50" s="109" t="n"/>
-      <c r="M50" s="80" t="inlineStr">
-        <is>
-          <t>Terminal value × terminal-year discount factor</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="6" customHeight="1">
-      <c r="A51" s="42" t="n"/>
-      <c r="B51" s="42" t="n"/>
-      <c r="C51" s="42" t="n"/>
-      <c r="D51" s="42" t="n"/>
-      <c r="E51" s="42" t="n"/>
-      <c r="F51" s="42" t="n"/>
-      <c r="G51" s="42" t="n"/>
-      <c r="H51" s="42" t="n"/>
-      <c r="I51" s="42" t="n"/>
-      <c r="J51" s="42" t="n"/>
-      <c r="K51" s="42" t="n"/>
-      <c r="L51" s="42" t="n"/>
-      <c r="M51" s="42" t="n"/>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="50" ht="6" customHeight="1">
+      <c r="A50" s="42" t="n"/>
+      <c r="B50" s="42" t="n"/>
+      <c r="C50" s="42" t="n"/>
+      <c r="D50" s="42" t="n"/>
+      <c r="E50" s="42" t="n"/>
+      <c r="F50" s="42" t="n"/>
+      <c r="G50" s="42" t="n"/>
+      <c r="H50" s="42" t="n"/>
+      <c r="I50" s="42" t="n"/>
+      <c r="J50" s="42" t="n"/>
+      <c r="K50" s="42" t="n"/>
+      <c r="L50" s="42" t="n"/>
+      <c r="M50" s="42" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>SECTION 6 — EQUITY VALUE BRIDGE  &amp;  IMPLIED SHARE PRICE</t>
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="73" t="inlineStr">
+        <is>
+          <t>Enterprise Value  [Gordon Growth]</t>
+        </is>
+      </c>
+      <c r="B52" s="90">
+        <f>B47+B48</f>
+        <v/>
+      </c>
+      <c r="C52" s="99" t="n"/>
+      <c r="D52" s="99" t="n"/>
+      <c r="E52" s="99" t="n"/>
+      <c r="F52" s="99" t="n"/>
+      <c r="G52" s="99" t="n"/>
+      <c r="H52" s="99" t="n"/>
+      <c r="I52" s="99" t="n"/>
+      <c r="J52" s="99" t="n"/>
+      <c r="K52" s="99" t="n"/>
+      <c r="L52" s="99" t="n"/>
+      <c r="M52" s="99" t="n"/>
+    </row>
     <row r="53">
-      <c r="A53" s="75" t="inlineStr">
-        <is>
-          <t>Enterprise Value  [Gordon Growth]</t>
-        </is>
-      </c>
-      <c r="B53" s="95">
-        <f>B48+B49</f>
-        <v/>
-      </c>
-      <c r="C53" s="104" t="n"/>
-      <c r="D53" s="104" t="n"/>
-      <c r="E53" s="104" t="n"/>
-      <c r="F53" s="104" t="n"/>
-      <c r="G53" s="104" t="n"/>
-      <c r="H53" s="104" t="n"/>
-      <c r="I53" s="104" t="n"/>
-      <c r="J53" s="104" t="n"/>
-      <c r="K53" s="104" t="n"/>
-      <c r="L53" s="104" t="n"/>
-      <c r="M53" s="104" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="75" t="inlineStr">
+      <c r="A53" s="73" t="inlineStr">
         <is>
           <t>Enterprise Value  [Exit Multiple]</t>
         </is>
       </c>
-      <c r="B54" s="95">
-        <f>B48+B50</f>
-        <v/>
-      </c>
-      <c r="C54" s="104" t="n"/>
-      <c r="D54" s="104" t="n"/>
-      <c r="E54" s="104" t="n"/>
-      <c r="F54" s="104" t="n"/>
-      <c r="G54" s="104" t="n"/>
-      <c r="H54" s="104" t="n"/>
-      <c r="I54" s="104" t="n"/>
-      <c r="J54" s="104" t="n"/>
-      <c r="K54" s="104" t="n"/>
-      <c r="L54" s="104" t="n"/>
-      <c r="M54" s="104" t="n"/>
+      <c r="B53" s="90">
+        <f>B47+B49</f>
+        <v/>
+      </c>
+      <c r="C53" s="99" t="n"/>
+      <c r="D53" s="99" t="n"/>
+      <c r="E53" s="99" t="n"/>
+      <c r="F53" s="99" t="n"/>
+      <c r="G53" s="99" t="n"/>
+      <c r="H53" s="99" t="n"/>
+      <c r="I53" s="99" t="n"/>
+      <c r="J53" s="99" t="n"/>
+      <c r="K53" s="99" t="n"/>
+      <c r="L53" s="99" t="n"/>
+      <c r="M53" s="99" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: Net Debt  (Debt − Cash)</t>
+        </is>
+      </c>
+      <c r="B54" s="97">
+        <f>'Balance Sheet'!F81</f>
+        <v/>
+      </c>
+      <c r="C54" s="98" t="n"/>
+      <c r="D54" s="98" t="n"/>
+      <c r="E54" s="98" t="n"/>
+      <c r="F54" s="98" t="n"/>
+      <c r="G54" s="98" t="n"/>
+      <c r="H54" s="98" t="n"/>
+      <c r="I54" s="98" t="n"/>
+      <c r="J54" s="98" t="n"/>
+      <c r="K54" s="98" t="n"/>
+      <c r="L54" s="98" t="n"/>
+      <c r="M54" s="77" t="inlineStr">
+        <is>
+          <t>Linked from Balance Sheet: Total Debt (ST+LT) − Cash &amp; Equivalents  (negative = net cash)</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Less: Net Debt  (Debt − Cash)</t>
-        </is>
-      </c>
-      <c r="B55" s="102">
-        <f>'Balance Sheet'!F81</f>
-        <v/>
-      </c>
-      <c r="C55" s="103" t="n"/>
-      <c r="D55" s="103" t="n"/>
-      <c r="E55" s="103" t="n"/>
-      <c r="F55" s="103" t="n"/>
-      <c r="G55" s="103" t="n"/>
-      <c r="H55" s="103" t="n"/>
-      <c r="I55" s="103" t="n"/>
-      <c r="J55" s="103" t="n"/>
-      <c r="K55" s="103" t="n"/>
-      <c r="L55" s="103" t="n"/>
-      <c r="M55" s="80" t="inlineStr">
-        <is>
-          <t>Linked from Balance Sheet: Total Debt (ST+LT) − Cash &amp; Equivalents  (negative = net cash)</t>
+      <c r="A55" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: Minority Interest</t>
+        </is>
+      </c>
+      <c r="B55" s="97" t="n">
+        <v>728</v>
+      </c>
+      <c r="C55" s="98" t="n"/>
+      <c r="D55" s="98" t="n"/>
+      <c r="E55" s="98" t="n"/>
+      <c r="F55" s="98" t="n"/>
+      <c r="G55" s="98" t="n"/>
+      <c r="H55" s="98" t="n"/>
+      <c r="I55" s="98" t="n"/>
+      <c r="J55" s="98" t="n"/>
+      <c r="K55" s="98" t="n"/>
+      <c r="L55" s="98" t="n"/>
+      <c r="M55" s="77" t="inlineStr">
+        <is>
+          <t>Auto-linked from Balance Sheet: minorityInterest</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Less: Minority Interest</t>
-        </is>
-      </c>
-      <c r="B56" s="102" t="n">
-        <v>728</v>
-      </c>
-      <c r="C56" s="103" t="n"/>
-      <c r="D56" s="103" t="n"/>
-      <c r="E56" s="103" t="n"/>
-      <c r="F56" s="103" t="n"/>
-      <c r="G56" s="103" t="n"/>
-      <c r="H56" s="103" t="n"/>
-      <c r="I56" s="103" t="n"/>
-      <c r="J56" s="103" t="n"/>
-      <c r="K56" s="103" t="n"/>
-      <c r="L56" s="103" t="n"/>
-      <c r="M56" s="80" t="inlineStr">
-        <is>
-          <t>Auto-linked from Balance Sheet: minorityInterest</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="89" t="inlineStr">
+      <c r="A56" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">  Shares Outstanding — Diluted  (mm)</t>
         </is>
       </c>
-      <c r="B57" s="102" t="n">
+      <c r="B56" s="97" t="n">
         <v>3528</v>
       </c>
-      <c r="C57" s="103" t="n"/>
-      <c r="D57" s="103" t="n"/>
-      <c r="E57" s="103" t="n"/>
-      <c r="F57" s="103" t="n"/>
-      <c r="G57" s="103" t="n"/>
-      <c r="H57" s="103" t="n"/>
-      <c r="I57" s="103" t="n"/>
-      <c r="J57" s="103" t="n"/>
-      <c r="K57" s="103" t="n"/>
-      <c r="L57" s="103" t="n"/>
-      <c r="M57" s="80" t="inlineStr">
+      <c r="C56" s="98" t="n"/>
+      <c r="D56" s="98" t="n"/>
+      <c r="E56" s="98" t="n"/>
+      <c r="F56" s="98" t="n"/>
+      <c r="G56" s="98" t="n"/>
+      <c r="H56" s="98" t="n"/>
+      <c r="I56" s="98" t="n"/>
+      <c r="J56" s="98" t="n"/>
+      <c r="K56" s="98" t="n"/>
+      <c r="L56" s="98" t="n"/>
+      <c r="M56" s="77" t="inlineStr">
         <is>
           <t>Auto-linked: weightedAverageShsOutDil from income statement (diluted)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="6" customHeight="1">
-      <c r="A58" s="42" t="n"/>
-      <c r="B58" s="42" t="n"/>
-      <c r="C58" s="42" t="n"/>
-      <c r="D58" s="42" t="n"/>
-      <c r="E58" s="42" t="n"/>
-      <c r="F58" s="42" t="n"/>
-      <c r="G58" s="42" t="n"/>
-      <c r="H58" s="42" t="n"/>
-      <c r="I58" s="42" t="n"/>
-      <c r="J58" s="42" t="n"/>
-      <c r="K58" s="42" t="n"/>
-      <c r="L58" s="42" t="n"/>
-      <c r="M58" s="42" t="n"/>
+    <row r="57" ht="6" customHeight="1">
+      <c r="A57" s="42" t="n"/>
+      <c r="B57" s="42" t="n"/>
+      <c r="C57" s="42" t="n"/>
+      <c r="D57" s="42" t="n"/>
+      <c r="E57" s="42" t="n"/>
+      <c r="F57" s="42" t="n"/>
+      <c r="G57" s="42" t="n"/>
+      <c r="H57" s="42" t="n"/>
+      <c r="I57" s="42" t="n"/>
+      <c r="J57" s="42" t="n"/>
+      <c r="K57" s="42" t="n"/>
+      <c r="L57" s="42" t="n"/>
+      <c r="M57" s="42" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="73" t="inlineStr">
+        <is>
+          <t>Implied Share Price  [Gordon Growth]  ($)</t>
+        </is>
+      </c>
+      <c r="B58" s="105">
+        <f>IFERROR((B52-B54-B55)/B56,"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="99" t="n"/>
+      <c r="D58" s="99" t="n"/>
+      <c r="E58" s="99" t="n"/>
+      <c r="F58" s="99" t="n"/>
+      <c r="G58" s="99" t="n"/>
+      <c r="H58" s="99" t="n"/>
+      <c r="I58" s="99" t="n"/>
+      <c r="J58" s="99" t="n"/>
+      <c r="K58" s="99" t="n"/>
+      <c r="L58" s="99" t="n"/>
+      <c r="M58" s="99" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="75" t="inlineStr">
-        <is>
-          <t>Implied Share Price  [Gordon Growth]  ($)</t>
-        </is>
-      </c>
-      <c r="B59" s="110">
-        <f>IFERROR((B53-B55-B56)/B57,"")</f>
-        <v/>
-      </c>
-      <c r="C59" s="104" t="n"/>
-      <c r="D59" s="104" t="n"/>
-      <c r="E59" s="104" t="n"/>
-      <c r="F59" s="104" t="n"/>
-      <c r="G59" s="104" t="n"/>
-      <c r="H59" s="104" t="n"/>
-      <c r="I59" s="104" t="n"/>
-      <c r="J59" s="104" t="n"/>
-      <c r="K59" s="104" t="n"/>
-      <c r="L59" s="104" t="n"/>
-      <c r="M59" s="104" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="75" t="inlineStr">
+      <c r="A59" s="73" t="inlineStr">
         <is>
           <t>Implied Share Price  [Exit Multiple]  ($)</t>
         </is>
       </c>
-      <c r="B60" s="110">
-        <f>IFERROR((B54-B55-B56)/B57,"")</f>
-        <v/>
-      </c>
-      <c r="C60" s="104" t="n"/>
-      <c r="D60" s="104" t="n"/>
-      <c r="E60" s="104" t="n"/>
-      <c r="F60" s="104" t="n"/>
-      <c r="G60" s="104" t="n"/>
-      <c r="H60" s="104" t="n"/>
-      <c r="I60" s="104" t="n"/>
-      <c r="J60" s="104" t="n"/>
-      <c r="K60" s="104" t="n"/>
-      <c r="L60" s="104" t="n"/>
-      <c r="M60" s="104" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="101" t="inlineStr">
+      <c r="B59" s="105">
+        <f>IFERROR((B53-B54-B55)/B56,"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="99" t="n"/>
+      <c r="D59" s="99" t="n"/>
+      <c r="E59" s="99" t="n"/>
+      <c r="F59" s="99" t="n"/>
+      <c r="G59" s="99" t="n"/>
+      <c r="H59" s="99" t="n"/>
+      <c r="I59" s="99" t="n"/>
+      <c r="J59" s="99" t="n"/>
+      <c r="K59" s="99" t="n"/>
+      <c r="L59" s="99" t="n"/>
+      <c r="M59" s="99" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="96" t="inlineStr">
         <is>
           <t>Current Market Price  ($)</t>
         </is>
       </c>
-      <c r="B61" s="111" t="n">
+      <c r="B60" s="106" t="n">
         <v>426.01</v>
       </c>
-      <c r="C61" s="103" t="n"/>
-      <c r="D61" s="103" t="n"/>
-      <c r="E61" s="103" t="n"/>
-      <c r="F61" s="103" t="n"/>
-      <c r="G61" s="103" t="n"/>
-      <c r="H61" s="103" t="n"/>
-      <c r="I61" s="103" t="n"/>
-      <c r="J61" s="103" t="n"/>
-      <c r="K61" s="103" t="n"/>
-      <c r="L61" s="103" t="n"/>
-      <c r="M61" s="80" t="inlineStr">
+      <c r="C60" s="98" t="n"/>
+      <c r="D60" s="98" t="n"/>
+      <c r="E60" s="98" t="n"/>
+      <c r="F60" s="98" t="n"/>
+      <c r="G60" s="98" t="n"/>
+      <c r="H60" s="98" t="n"/>
+      <c r="I60" s="98" t="n"/>
+      <c r="J60" s="98" t="n"/>
+      <c r="K60" s="98" t="n"/>
+      <c r="L60" s="98" t="n"/>
+      <c r="M60" s="77" t="inlineStr">
         <is>
           <t>Auto-linked from FMP company profile — price</t>
         </is>
       </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>Upside / (Downside)  [Gordon Growth]</t>
+        </is>
+      </c>
+      <c r="B61" s="107">
+        <f>IFERROR(B58/B60-1,"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="104" t="n"/>
+      <c r="D61" s="104" t="n"/>
+      <c r="E61" s="104" t="n"/>
+      <c r="F61" s="104" t="n"/>
+      <c r="G61" s="104" t="n"/>
+      <c r="H61" s="104" t="n"/>
+      <c r="I61" s="104" t="n"/>
+      <c r="J61" s="104" t="n"/>
+      <c r="K61" s="104" t="n"/>
+      <c r="L61" s="104" t="n"/>
+      <c r="M61" s="104" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="63" t="inlineStr">
         <is>
-          <t>Upside / (Downside)  [Gordon Growth]</t>
-        </is>
-      </c>
-      <c r="B62" s="112">
-        <f>IFERROR(B59/B61-1,"")</f>
-        <v/>
-      </c>
-      <c r="C62" s="109" t="n"/>
-      <c r="D62" s="109" t="n"/>
-      <c r="E62" s="109" t="n"/>
-      <c r="F62" s="109" t="n"/>
-      <c r="G62" s="109" t="n"/>
-      <c r="H62" s="109" t="n"/>
-      <c r="I62" s="109" t="n"/>
-      <c r="J62" s="109" t="n"/>
-      <c r="K62" s="109" t="n"/>
-      <c r="L62" s="109" t="n"/>
-      <c r="M62" s="109" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="63" t="inlineStr">
-        <is>
           <t>Upside / (Downside)  [Exit Multiple]</t>
         </is>
       </c>
-      <c r="B63" s="112">
-        <f>IFERROR(B60/B61-1,"")</f>
-        <v/>
-      </c>
-      <c r="C63" s="109" t="n"/>
-      <c r="D63" s="109" t="n"/>
-      <c r="E63" s="109" t="n"/>
-      <c r="F63" s="109" t="n"/>
-      <c r="G63" s="109" t="n"/>
-      <c r="H63" s="109" t="n"/>
-      <c r="I63" s="109" t="n"/>
-      <c r="J63" s="109" t="n"/>
-      <c r="K63" s="109" t="n"/>
-      <c r="L63" s="109" t="n"/>
-      <c r="M63" s="109" t="n"/>
+      <c r="B62" s="107">
+        <f>IFERROR(B59/B60-1,"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="104" t="n"/>
+      <c r="D62" s="104" t="n"/>
+      <c r="E62" s="104" t="n"/>
+      <c r="F62" s="104" t="n"/>
+      <c r="G62" s="104" t="n"/>
+      <c r="H62" s="104" t="n"/>
+      <c r="I62" s="104" t="n"/>
+      <c r="J62" s="104" t="n"/>
+      <c r="K62" s="104" t="n"/>
+      <c r="L62" s="104" t="n"/>
+      <c r="M62" s="104" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A44:M44"/>
+  <mergeCells count="8">
+    <mergeCell ref="A13:M13"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A34:M34"/>
+    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A52:M52"/>
+    <mergeCell ref="A51:M51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10039,14 +10021,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="113" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>JS SCORECARD — TSLA  |  Master Prompt v2  |  23 Jun 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="114" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>Blue rows = auto-scored (FMP data + yfinance proxies).  Yellow rows = manual — select tier from dropdown in column E.  Only 2 criteria require manual input: Business Clarity + Long-Term Potential.  Score: HIGH=10 | MOD-HIGH=7 | MOD-LOW=3 | LOW=0</t>
         </is>
@@ -10063,7 +10045,7 @@
       <c r="H3" s="42" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="115" t="inlineStr">
+      <c r="A4" s="110" t="inlineStr">
         <is>
           <t>✓  No floor cap (D/EBITDA and EBIT/Interest within safe thresholds)</t>
         </is>
@@ -10080,42 +10062,42 @@
       <c r="H5" s="42" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="116" t="inlineStr">
+      <c r="A6" s="111" t="inlineStr">
         <is>
           <t>CRITERION</t>
         </is>
       </c>
-      <c r="B6" s="117" t="inlineStr">
+      <c r="B6" s="112" t="inlineStr">
         <is>
           <t>PART</t>
         </is>
       </c>
-      <c r="C6" s="117" t="inlineStr">
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>WEIGHT %</t>
         </is>
       </c>
-      <c r="D6" s="117" t="inlineStr">
+      <c r="D6" s="112" t="inlineStr">
         <is>
           <t>CALCULATED VALUE</t>
         </is>
       </c>
-      <c r="E6" s="117" t="inlineStr">
+      <c r="E6" s="112" t="inlineStr">
         <is>
           <t>TIER  ▼</t>
         </is>
       </c>
-      <c r="F6" s="117" t="inlineStr">
+      <c r="F6" s="112" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
       </c>
-      <c r="G6" s="117" t="inlineStr">
+      <c r="G6" s="112" t="inlineStr">
         <is>
           <t>WTD SCORE</t>
         </is>
       </c>
-      <c r="H6" s="116" t="inlineStr">
+      <c r="H6" s="111" t="inlineStr">
         <is>
           <t>NOTES / COMMENTARY (editable)</t>
         </is>
@@ -10129,134 +10111,134 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="118" t="inlineStr">
+      <c r="A8" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">  Business Clarity</t>
         </is>
       </c>
-      <c r="B8" s="119" t="inlineStr">
+      <c r="B8" s="114" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C8" s="120" t="n">
+      <c r="C8" s="115" t="n">
         <v>0.025</v>
       </c>
-      <c r="D8" s="121" t="inlineStr">
+      <c r="D8" s="116" t="inlineStr">
         <is>
           <t>— user input required</t>
         </is>
       </c>
-      <c r="E8" s="122" t="n"/>
-      <c r="F8" s="123">
+      <c r="E8" s="117" t="n"/>
+      <c r="F8" s="118">
         <f>IF(E8="HIGH",10,IF(E8="MOD-HIGH",7,IF(E8="MOD-LOW",3,IF(E8="LOW",0,""))))</f>
         <v/>
       </c>
-      <c r="G8" s="124">
+      <c r="G8" s="119">
         <f>IF(F8="",0,C8*F8*10)</f>
         <v/>
       </c>
-      <c r="H8" s="125" t="inlineStr"/>
+      <c r="H8" s="120" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="126" t="inlineStr">
+      <c r="A9" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Moat Profile</t>
         </is>
       </c>
-      <c r="B9" s="127" t="inlineStr">
+      <c r="B9" s="122" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C9" s="128" t="n">
+      <c r="C9" s="123" t="n">
         <v>0.1</v>
       </c>
-      <c r="D9" s="129" t="inlineStr">
+      <c r="D9" s="124" t="inlineStr">
         <is>
           <t>GM 18.0% ✗ (&gt;40%)  |  GM trend -7.6% ✗ (&gt;+1pp)  |  ROIC-WACC -7.9% ✗ (&gt;+5pp)  |  Rev consistency σ=21.4% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
         </is>
       </c>
-      <c r="E9" s="130" t="inlineStr">
+      <c r="E9" s="125" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F9" s="131" t="n">
+      <c r="F9" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="132">
+      <c r="G9" s="127">
         <f>IF(F9="",0,C9*F9*10)</f>
         <v/>
       </c>
-      <c r="H9" s="133" t="inlineStr">
+      <c r="H9" s="128" t="inlineStr">
         <is>
           <t>GM 18.0% ✗ (&gt;40%)  |  GM trend -7.6% ✗ (&gt;+1pp)  |  ROIC-WACC -7.9% ✗ (&gt;+5pp)  |  Rev consistency σ=21.4% ✗ (&lt;8%)  [0/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="118" t="inlineStr">
+      <c r="A10" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">  Long-Term Potential</t>
         </is>
       </c>
-      <c r="B10" s="119" t="inlineStr">
+      <c r="B10" s="114" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C10" s="120" t="n">
+      <c r="C10" s="115" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" s="121" t="inlineStr">
+      <c r="D10" s="116" t="inlineStr">
         <is>
           <t>— user input required</t>
         </is>
       </c>
-      <c r="E10" s="122" t="n"/>
-      <c r="F10" s="123">
+      <c r="E10" s="117" t="n"/>
+      <c r="F10" s="118">
         <f>IF(E10="HIGH",10,IF(E10="MOD-HIGH",7,IF(E10="MOD-LOW",3,IF(E10="LOW",0,""))))</f>
         <v/>
       </c>
-      <c r="G10" s="124">
+      <c r="G10" s="119">
         <f>IF(F10="",0,C10*F10*10)</f>
         <v/>
       </c>
-      <c r="H10" s="125" t="inlineStr"/>
+      <c r="H10" s="120" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="126" t="inlineStr">
+      <c r="A11" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Management</t>
         </is>
       </c>
-      <c r="B11" s="127" t="inlineStr">
+      <c r="B11" s="122" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C11" s="128" t="n">
+      <c r="C11" s="123" t="n">
         <v>0.075</v>
       </c>
-      <c r="D11" s="129" t="inlineStr">
+      <c r="D11" s="124" t="inlineStr">
         <is>
           <t>ROIC trend -36.8% ✗ (&gt;=-2pp)  |  GM maintained -7.6% ✗  |  Op margin -12.2% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count +2.2%/yr ✗ (≤+2%/yr)  |  Goodwill/Equity 0% ✓ (&lt;40%)  [1/6 indicators positive — proxy score]</t>
         </is>
       </c>
-      <c r="E11" s="130" t="inlineStr">
+      <c r="E11" s="125" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F11" s="131" t="n">
+      <c r="F11" s="126" t="n">
         <v>1.67</v>
       </c>
-      <c r="G11" s="132">
+      <c r="G11" s="127">
         <f>IF(F11="",0,C11*F11*10)</f>
         <v/>
       </c>
-      <c r="H11" s="133" t="inlineStr">
+      <c r="H11" s="128" t="inlineStr">
         <is>
           <t>ROIC trend -36.8% ✗ (&gt;=-2pp)  |  GM maintained -7.6% ✗  |  Op margin -12.2% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count +2.2%/yr ✗ (≤+2%/yr)  |  Goodwill/Equity 0% ✓ (&lt;40%)  [1/6 indicators positive — proxy score]</t>
         </is>
@@ -10270,148 +10252,148 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="126" t="inlineStr">
+      <c r="A13" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue 3yr CAGR</t>
         </is>
       </c>
-      <c r="B13" s="127" t="inlineStr">
+      <c r="B13" s="122" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C13" s="128" t="n">
+      <c r="C13" s="123" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" s="129" t="inlineStr">
+      <c r="D13" s="124" t="inlineStr">
         <is>
           <t>5.2%</t>
         </is>
       </c>
-      <c r="E13" s="130" t="inlineStr">
+      <c r="E13" s="125" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F13" s="131" t="n">
+      <c r="F13" s="126" t="n">
         <v>2.6</v>
       </c>
-      <c r="G13" s="132">
+      <c r="G13" s="127">
         <f>IF(F13="",0,C13*F13*10)</f>
         <v/>
       </c>
-      <c r="H13" s="133" t="inlineStr">
+      <c r="H13" s="128" t="inlineStr">
         <is>
           <t>5.2%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="126" t="inlineStr">
+      <c r="A14" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cash Quality  (FCF / Net Income)</t>
         </is>
       </c>
-      <c r="B14" s="127" t="inlineStr">
+      <c r="B14" s="122" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C14" s="128" t="n">
+      <c r="C14" s="123" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" s="129" t="inlineStr">
+      <c r="D14" s="124" t="inlineStr">
         <is>
           <t>133%  [through-cycle: 70/30 latest+5yr median, latest 163.9% → smoothed 132.8%]</t>
         </is>
       </c>
-      <c r="E14" s="134" t="inlineStr">
+      <c r="E14" s="129" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F14" s="131" t="n">
+      <c r="F14" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="132">
+      <c r="G14" s="127">
         <f>IF(F14="",0,C14*F14*10)</f>
         <v/>
       </c>
-      <c r="H14" s="133" t="inlineStr">
+      <c r="H14" s="128" t="inlineStr">
         <is>
           <t>133%  [through-cycle: 70/30 latest+5yr median, latest 163.9% → smoothed 132.8%]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="126" t="inlineStr">
+      <c r="A15" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capital Returns</t>
         </is>
       </c>
-      <c r="B15" s="127" t="inlineStr">
+      <c r="B15" s="122" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C15" s="128" t="n">
+      <c r="C15" s="123" t="n">
         <v>0.05</v>
       </c>
-      <c r="D15" s="129" t="inlineStr">
+      <c r="D15" s="124" t="inlineStr">
         <is>
           <t>No capital returns in latest year</t>
         </is>
       </c>
-      <c r="E15" s="130" t="inlineStr">
+      <c r="E15" s="125" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F15" s="131" t="n">
+      <c r="F15" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="132">
+      <c r="G15" s="127">
         <f>IF(F15="",0,C15*F15*10)</f>
         <v/>
       </c>
-      <c r="H15" s="133" t="inlineStr">
+      <c r="H15" s="128" t="inlineStr">
         <is>
           <t>No capital returns in latest year</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="126" t="inlineStr">
+      <c r="A16" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  ROIC</t>
         </is>
       </c>
-      <c r="B16" s="127" t="inlineStr">
+      <c r="B16" s="122" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C16" s="128" t="n">
+      <c r="C16" s="123" t="n">
         <v>0.075</v>
       </c>
-      <c r="D16" s="129" t="inlineStr">
+      <c r="D16" s="124" t="inlineStr">
         <is>
           <t>5.6%  [trend penalty: declined &gt;5pp vs 3yr ago]  [through-cycle: 70/30 latest+5yr median, latest 4.3% → smoothed 5.6%]</t>
         </is>
       </c>
-      <c r="E16" s="130" t="inlineStr">
+      <c r="E16" s="125" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F16" s="131" t="n">
+      <c r="F16" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="132">
+      <c r="G16" s="127">
         <f>IF(F16="",0,C16*F16*10)</f>
         <v/>
       </c>
-      <c r="H16" s="133" t="inlineStr">
+      <c r="H16" s="128" t="inlineStr">
         <is>
           <t>5.6%  [trend penalty: declined &gt;5pp vs 3yr ago]  [through-cycle: 70/30 latest+5yr median, latest 4.3% → smoothed 5.6%]</t>
         </is>
@@ -10425,111 +10407,111 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="126" t="inlineStr">
+      <c r="A18" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
         </is>
       </c>
-      <c r="B18" s="127" t="inlineStr">
+      <c r="B18" s="122" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C18" s="128" t="n">
+      <c r="C18" s="123" t="n">
         <v>0.05</v>
       </c>
-      <c r="D18" s="129" t="inlineStr">
+      <c r="D18" s="124" t="inlineStr">
         <is>
           <t>Net cash $8,137mm — no net leverage  [through-cycle: 70/30 latest+5yr median, latest 0.7x → smoothed 0.7x]</t>
         </is>
       </c>
-      <c r="E18" s="134" t="inlineStr">
+      <c r="E18" s="129" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F18" s="131" t="n">
+      <c r="F18" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="132">
+      <c r="G18" s="127">
         <f>IF(F18="",0,C18*F18*10)</f>
         <v/>
       </c>
-      <c r="H18" s="133" t="inlineStr">
+      <c r="H18" s="128" t="inlineStr">
         <is>
           <t>Net cash $8,137mm — no net leverage  [through-cycle: 70/30 latest+5yr median, latest 0.7x → smoothed 0.7x]</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="126" t="inlineStr">
+      <c r="A19" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Interest Cover  (EBIT / Interest)</t>
         </is>
       </c>
-      <c r="B19" s="127" t="inlineStr">
+      <c r="B19" s="122" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C19" s="128" t="n">
+      <c r="C19" s="123" t="n">
         <v>0.075</v>
       </c>
-      <c r="D19" s="129" t="inlineStr">
+      <c r="D19" s="124" t="inlineStr">
         <is>
           <t>12.9x</t>
         </is>
       </c>
-      <c r="E19" s="134" t="inlineStr">
+      <c r="E19" s="129" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F19" s="131" t="n">
+      <c r="F19" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="132">
+      <c r="G19" s="127">
         <f>IF(F19="",0,C19*F19*10)</f>
         <v/>
       </c>
-      <c r="H19" s="133" t="inlineStr">
+      <c r="H19" s="128" t="inlineStr">
         <is>
           <t>12.9x</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="126" t="inlineStr">
+      <c r="A20" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Execution Risk</t>
         </is>
       </c>
-      <c r="B20" s="127" t="inlineStr">
+      <c r="B20" s="122" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C20" s="128" t="n">
+      <c r="C20" s="123" t="n">
         <v>0.05</v>
       </c>
-      <c r="D20" s="129" t="inlineStr">
+      <c r="D20" s="124" t="inlineStr">
         <is>
           <t>Rev growth σ=21.4%  |  OM trend -7.5%, σ=4.2%  [quality = direction + stability]</t>
         </is>
       </c>
-      <c r="E20" s="130" t="inlineStr">
+      <c r="E20" s="125" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F20" s="131" t="n">
+      <c r="F20" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="132">
+      <c r="G20" s="127">
         <f>IF(F20="",0,C20*F20*10)</f>
         <v/>
       </c>
-      <c r="H20" s="133" t="inlineStr">
+      <c r="H20" s="128" t="inlineStr">
         <is>
           <t>Rev growth σ=21.4%  |  OM trend -7.5%, σ=4.2%  [quality = direction + stability]</t>
         </is>
@@ -10543,76 +10525,76 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="126" t="inlineStr">
+      <c r="A22" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation vs Median  (P/E)</t>
         </is>
       </c>
-      <c r="B22" s="127" t="inlineStr">
+      <c r="B22" s="122" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C22" s="128" t="n">
+      <c r="C22" s="123" t="n">
         <v>0.1</v>
       </c>
-      <c r="D22" s="129" t="inlineStr">
-        <is>
-          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 212.8x  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
-      <c r="E22" s="130" t="inlineStr">
+      <c r="D22" s="124" t="inlineStr">
+        <is>
+          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 215.0x  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
+        </is>
+      </c>
+      <c r="E22" s="125" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F22" s="131" t="n">
+      <c r="F22" s="126" t="n">
         <v>0.5</v>
       </c>
-      <c r="G22" s="132">
+      <c r="G22" s="127">
         <f>IF(F22="",0,C22*F22*10)</f>
         <v/>
       </c>
-      <c r="H22" s="133" t="inlineStr">
-        <is>
-          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 212.8x  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
+      <c r="H22" s="128" t="inlineStr">
+        <is>
+          <t>Fwd P/E 223.8x (scoring basis)  |  5yr avg 215.0x  [+348% vs benchmark]  [trail=0.00 | fwd_pe=223.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  PEG=362.05 (fwd_pe=223.8x / eps_growth=62%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="126" t="inlineStr">
+      <c r="A23" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation vs Median  (P/FCF)</t>
         </is>
       </c>
-      <c r="B23" s="127" t="inlineStr">
+      <c r="B23" s="122" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C23" s="128" t="n">
+      <c r="C23" s="123" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="129" t="inlineStr">
-        <is>
-          <t>Current 233.2x  |  5yr avg 227.9x  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.5%  spread=-4.0%→modifier=-0.50]</t>
-        </is>
-      </c>
-      <c r="E23" s="130" t="inlineStr">
+      <c r="D23" s="124" t="inlineStr">
+        <is>
+          <t>Current 233.2x  |  5yr avg 229.0x  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.5%  spread=-4.0%→modifier=-0.50]</t>
+        </is>
+      </c>
+      <c r="E23" s="125" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F23" s="131" t="n">
+      <c r="F23" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="132">
+      <c r="G23" s="127">
         <f>IF(F23="",0,C23*F23*10)</f>
         <v/>
       </c>
-      <c r="H23" s="133" t="inlineStr">
-        <is>
-          <t>Current 233.2x  |  5yr avg 227.9x  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.5%  spread=-4.0%→modifier=-0.50]</t>
+      <c r="H23" s="128" t="inlineStr">
+        <is>
+          <t>Current 233.2x  |  5yr avg 229.0x  [+366% vs benchmark]  [trail=0.00 | fwd_pfcf=203.8x→0.00 | abs=0.0 → blended 40/40/20=0.00]  [fcf_yield=0.4% vs rf=4.5%  spread=-4.0%→modifier=-0.50]</t>
         </is>
       </c>
     </row>
@@ -10627,21 +10609,21 @@
       <c r="H24" s="42" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="135" t="inlineStr">
+      <c r="A25" s="130" t="inlineStr">
         <is>
           <t>TOTAL SCORE  (max = 100.0)</t>
         </is>
       </c>
-      <c r="B25" s="136" t="n"/>
-      <c r="C25" s="136" t="n"/>
-      <c r="D25" s="136" t="n"/>
-      <c r="E25" s="136" t="n"/>
-      <c r="F25" s="136" t="n"/>
-      <c r="G25" s="137">
+      <c r="B25" s="131" t="n"/>
+      <c r="C25" s="131" t="n"/>
+      <c r="D25" s="131" t="n"/>
+      <c r="E25" s="131" t="n"/>
+      <c r="F25" s="131" t="n"/>
+      <c r="G25" s="132">
         <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
         <v/>
       </c>
-      <c r="H25" s="138" t="inlineStr">
+      <c r="H25" s="133" t="inlineStr">
         <is>
           <t>No floor cap.</t>
         </is>
@@ -10658,7 +10640,7 @@
       <c r="H26" s="42" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="139">
+      <c r="A27" s="134">
         <f>IF(G25="","Score incomplete — fill qualitative tiers above",IF(G25&gt;=80,"STRONG BUY",IF(G25&gt;=65,"BUY",IF(G25&gt;=50,"HOLD",IF(G25&gt;=35,"REDUCE","SELL")))))</f>
         <v/>
       </c>
@@ -10674,7 +10656,7 @@
       <c r="H28" s="42" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="140" t="inlineStr">
+      <c r="A29" s="135" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>
